--- a/词表.xlsx
+++ b/词表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjliu\Desktop\GRE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GRE\GRE-wordlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B084B0-3B86-4FB0-8C85-A761ADDAAE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB0CEB0-828F-4DBB-97D8-2FCCC7C847DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="1923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="2170">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7742,6 +7742,1010 @@
   </si>
   <si>
     <t>gather, obtain, extract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umbrage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 生气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resentment, offense</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umbr - shadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chagrin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 失望, 沮丧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disappointment, vexation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abeyance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 暂停</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quiescense, suspension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alacrity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 乐意, 欣然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zeal, enthusiasm, celerity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulwark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 保护, 防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>safeguard, defense, protection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 小心的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cautious, circumspect, heedful, chary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contingent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. dependent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circumstantial, unccertain, situational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proprietary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 私有的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>private, exclusive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gregarious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 群居的, 爱社交的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>social</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lucrative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 能赚钱的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profitable, remunerative, rewarding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lucre 钱财</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exigent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 紧急的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pressing, urgent, imperative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>melodramatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 戏剧化的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>theatrical, histrionic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fortuitous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 意外的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>serendipitous, accidental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precocious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 早熟的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>egalitarian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 主张平等的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>democratic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 贪污的, 唯利是图的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crooked, corrupt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>innate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 天生的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intuitive, inherent, inborn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paradigmatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 模范的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>model, prototype, exemplary, archetypal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 不情愿的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loathe v. 厌恶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disinclined, reluctant, averse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feckless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 软弱的, 无效的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bootless, futile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>feck - feit do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>futile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 无效的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fruitless, pointless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impotent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 无能的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>powerless, helpless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stringent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 严格的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exacting, rigorous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ameliorate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 改善, 改进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mitigate, extenuate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buoy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 鼓励, 支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮漂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sustain, help, encourage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resonate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 对某人重要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ring, matter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>construe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 解释, 解读</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interpret, understand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 禁止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disallow, prohibit, enjoin, ban</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prescribe 开处方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>improvise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 即兴发挥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ad-lib, extemporize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquiesce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 默许, 接受</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accede, consent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chasten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 使内疚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curtail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 缩减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abbreviate, diminish, truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>relish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 享受</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>savor, enjoy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调味品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evince</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 显示, 表明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>betray, testify to, manifest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vanish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>disappear, evaporate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sanity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 神志清醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rationality, soundness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sythesis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 综合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fusion, combination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consensus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 共识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accord, unanimity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>discord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contention, tension, friction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>courteous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有礼貌的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>polite, civil, gracious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>courtesy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>churllish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 粗鲁的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boorish, ungracious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>austere</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 朴实无华的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spartan, stark, plain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grandiose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 浮夸的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pompous, bombastic, pretentious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 弯曲的
+adj. 狡诈的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>circuitous
+cunning, underhanded</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amorphous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 没有固定形状的, 无组织的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formless, nebulous, diffuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>articulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. v. 清晰表达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eloquent, fluent, enunciate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 亲密的
+v. 暗示, 间接指出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiar
+hint, imply</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diffuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 松散的
+v. 扩散</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unfocused, amorphous
+spread, scatter, disperse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 表达, 说出
+adj. 完全的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>voice
+absolute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subordinate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. adj. 次要的, （使）次要的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subject, secondary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fraught</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 令人焦虑的
+adj. 充满的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contentious, stressful
+charged with</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antecedent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 先前的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prior, preceding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dissipate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 驱散, 消散
+v. 浪费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attenuate, abate
+squander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 镇压, 平息
+v. 否决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suppress, quell
+annul, nullify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intrigue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 激起兴趣
+n. 密谋, 阴谋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fascinate, captivate
+scheme, conspiracy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>serene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 安静的, 宁静的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>serenade 小夜曲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tranquil, placid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seminal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 开创性的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>groundbreaking, original</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cerebral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cerebrum 大脑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 理智的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dispassionate, intellectual, analytical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emergent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 新兴的, 刚出现的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nascent, budding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abstemious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有节制的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temperate, ascetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conducive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>favorable, beneficial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jocular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 幽默的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>humorous, facetious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laudatory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 赞美的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complimentary, adulatory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>idiosyncratic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 独特的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>distinctive, atypical, peculiar, unorthodox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concrete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 具体的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>palpable, tangible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 先锋的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pioneering, experimental, unconventional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastidious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 挑剔苛刻的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>picky, finicky, meticulous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>erudite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 博学的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scholarly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ancillary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ancilla 女仆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 辅助的, 补充的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subsidiary, supplementary, incidental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tactless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impolitic, undiplomatic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 不明智的, 低情商的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>moribund</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 濒死的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dying, declining</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sketchy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 粗略的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rudimentary, superficial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retrograde</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 倒退的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outmoded, regressive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mercury retrograde 水逆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dacadent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 堕落的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>degenerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sporadic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 断断续续的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>occasional, intermittent, fitful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cunning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 狡猾的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>devious, crafty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doctrinaire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 教条的, 固执武断的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dogmatic, rigid, inflexible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vehement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 激烈的, 激动的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>impassioned, fervent, forceful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 可怕的, 严重的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dreadful, grave</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8080,14 +9084,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E757"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:E835"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.4140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.3984375" style="1" customWidth="1"/>
     <col min="4" max="4" width="35.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.265625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -8209,7 +9213,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28">
+    <row r="9" spans="1:5" ht="27.75">
       <c r="A9" s="1">
         <v>1008</v>
       </c>
@@ -8587,7 +9591,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="28">
+    <row r="36" spans="1:5" ht="27.75">
       <c r="A36" s="1">
         <v>1035</v>
       </c>
@@ -8721,7 +9725,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="28">
+    <row r="46" spans="1:5" ht="27.75">
       <c r="A46" s="1">
         <v>2010</v>
       </c>
@@ -10719,7 +11723,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="28">
+    <row r="208" spans="1:5" ht="27.75">
       <c r="A208" s="1">
         <v>7014</v>
       </c>
@@ -11055,7 +12059,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="42">
+    <row r="235" spans="1:4" ht="41.65">
       <c r="A235" s="1">
         <v>7041</v>
       </c>
@@ -11327,7 +12331,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="28">
+    <row r="257" spans="1:4" ht="27.75">
       <c r="A257" s="1">
         <v>8013</v>
       </c>
@@ -11817,7 +12821,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="28">
+    <row r="295" spans="1:5" ht="27.75">
       <c r="A295" s="1">
         <v>9009</v>
       </c>
@@ -11856,7 +12860,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="42">
+    <row r="298" spans="1:5" ht="41.65">
       <c r="A298" s="1">
         <v>9012</v>
       </c>
@@ -12816,7 +13820,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="28">
+    <row r="370" spans="1:5" ht="27.75">
       <c r="A370" s="1">
         <v>10042</v>
       </c>
@@ -13661,7 +14665,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="28">
+    <row r="428" spans="1:5" ht="27.75">
       <c r="A428" s="1">
         <v>12009</v>
       </c>
@@ -13801,7 +14805,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="28">
+    <row r="438" spans="1:5" ht="27.75">
       <c r="A438" s="1">
         <v>12019</v>
       </c>
@@ -14228,7 +15232,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="28">
+    <row r="467" spans="1:5" ht="27.75">
       <c r="A467" s="1">
         <v>13009</v>
       </c>
@@ -14552,7 +15556,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="28">
+    <row r="488" spans="1:5" ht="27.75">
       <c r="A488" s="1">
         <v>13030</v>
       </c>
@@ -14754,7 +15758,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="28">
+    <row r="502" spans="1:5" ht="27.75">
       <c r="A502" s="1">
         <v>13044</v>
       </c>
@@ -15848,7 +16852,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="28">
+    <row r="578" spans="1:5" ht="27.75">
       <c r="A578" s="1">
         <v>15029</v>
       </c>
@@ -17325,7 +18329,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="28">
+    <row r="679" spans="1:5" ht="27.75">
       <c r="A679" s="1">
         <v>17043</v>
       </c>
@@ -17816,7 +18820,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="713" spans="1:4" ht="28">
+    <row r="713" spans="1:4" ht="27.75">
       <c r="A713" s="1">
         <v>18031</v>
       </c>
@@ -18200,7 +19204,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="28">
+    <row r="740" spans="1:5" ht="27.75">
       <c r="A740" s="1">
         <v>19017</v>
       </c>
@@ -18270,7 +19274,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="28">
+    <row r="745" spans="1:5" ht="27.75">
       <c r="A745" s="1">
         <v>19022</v>
       </c>
@@ -18388,7 +19392,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="753" spans="1:4">
+    <row r="753" spans="1:5">
       <c r="A753" s="1">
         <v>19030</v>
       </c>
@@ -18402,7 +19406,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="754" spans="1:4">
+    <row r="754" spans="1:5">
       <c r="A754" s="1">
         <v>19031</v>
       </c>
@@ -18416,7 +19420,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="755" spans="1:4">
+    <row r="755" spans="1:5">
       <c r="A755" s="1">
         <v>19032</v>
       </c>
@@ -18430,7 +19434,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="756" spans="1:4">
+    <row r="756" spans="1:5">
       <c r="A756" s="1">
         <v>19033</v>
       </c>
@@ -18444,9 +19448,1092 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="757" spans="1:4">
+    <row r="757" spans="1:5">
       <c r="A757" s="1">
-        <v>19034</v>
+        <v>20001</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C757" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="758" spans="1:5">
+      <c r="A758" s="1">
+        <v>20002</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C758" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D758" s="1" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="759" spans="1:5">
+      <c r="A759" s="1">
+        <v>20003</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C759" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D759" s="1" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="760" spans="1:5">
+      <c r="A760" s="1">
+        <v>20004</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C760" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="D760" s="1" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="761" spans="1:5">
+      <c r="A761" s="1">
+        <v>20005</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C761" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D761" s="1" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="762" spans="1:5">
+      <c r="A762" s="1">
+        <v>20006</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C762" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D762" s="1" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="763" spans="1:5">
+      <c r="A763" s="1">
+        <v>20007</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C763" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="D763" s="1" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="764" spans="1:5">
+      <c r="A764" s="1">
+        <v>20008</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C764" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="765" spans="1:5">
+      <c r="A765" s="1">
+        <v>20009</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C765" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="766" spans="1:5">
+      <c r="A766" s="1">
+        <v>20010</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C766" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E766" s="1" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="767" spans="1:5">
+      <c r="A767" s="1">
+        <v>20011</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C767" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D767" s="1" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="768" spans="1:5">
+      <c r="A768" s="1">
+        <v>20012</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C768" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D768" s="1" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="769" spans="1:5">
+      <c r="A769" s="1">
+        <v>20013</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C769" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="770" spans="1:5">
+      <c r="A770" s="1">
+        <v>20014</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C770" s="1" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D770" s="1" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="771" spans="1:5">
+      <c r="A771" s="1">
+        <v>20015</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C771" s="1" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="772" spans="1:5">
+      <c r="A772" s="1">
+        <v>20016</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C772" s="1" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="773" spans="1:5">
+      <c r="A773" s="1">
+        <v>20017</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C773" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D773" s="1" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="774" spans="1:5">
+      <c r="A774" s="1">
+        <v>20018</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C774" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D774" s="1" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="775" spans="1:5">
+      <c r="A775" s="1">
+        <v>20019</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C775" s="1" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E775" s="1" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="776" spans="1:5">
+      <c r="A776" s="1">
+        <v>20020</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E776" s="1" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="777" spans="1:5">
+      <c r="A777" s="1">
+        <v>20021</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C777" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="778" spans="1:5">
+      <c r="A778" s="1">
+        <v>20022</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C778" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="779" spans="1:5">
+      <c r="A779" s="1">
+        <v>20023</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="780" spans="1:5">
+      <c r="A780" s="1">
+        <v>20024</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C780" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="781" spans="1:5">
+      <c r="A781" s="1">
+        <v>20025</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E781" s="1" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="782" spans="1:5">
+      <c r="A782" s="1">
+        <v>20026</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E782" s="1" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="783" spans="1:5">
+      <c r="A783" s="1">
+        <v>20027</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C783" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5">
+      <c r="A784" s="1">
+        <v>20028</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C784" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E784" s="1" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5">
+      <c r="A785" s="1">
+        <v>20029</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C785" s="1" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="786" spans="1:5">
+      <c r="A786" s="1">
+        <v>20030</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C786" s="1" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="787" spans="1:5">
+      <c r="A787" s="1">
+        <v>20031</v>
+      </c>
+      <c r="B787" s="1" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C787" s="1" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D787" s="1" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="788" spans="1:5">
+      <c r="A788" s="1">
+        <v>20032</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C788" s="1" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="789" spans="1:5">
+      <c r="A789" s="1">
+        <v>20033</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C789" s="1" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D789" s="1" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E789" s="1" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="790" spans="1:5">
+      <c r="A790" s="1">
+        <v>20034</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C790" s="1" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="791" spans="1:5">
+      <c r="A791" s="1">
+        <v>20035</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C791" s="1" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="792" spans="1:5">
+      <c r="A792" s="1">
+        <v>20036</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C792" s="1" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D792" s="1" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="793" spans="1:5">
+      <c r="A793" s="1">
+        <v>20037</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C793" s="1" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="794" spans="1:5">
+      <c r="A794" s="1">
+        <v>20038</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C794" s="1" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D794" s="1" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="795" spans="1:5">
+      <c r="A795" s="1">
+        <v>20039</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C795" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D795" s="1" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="796" spans="1:5">
+      <c r="A796" s="1">
+        <v>20040</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C796" s="1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E796" s="1" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="797" spans="1:5">
+      <c r="A797" s="1">
+        <v>20041</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C797" s="1" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D797" s="1" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="798" spans="1:5">
+      <c r="A798" s="1">
+        <v>20042</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C798" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D798" s="1" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="799" spans="1:5">
+      <c r="A799" s="1">
+        <v>20043</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C799" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D799" s="1" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="800" spans="1:5" ht="27.75">
+      <c r="A800" s="1">
+        <v>21001</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C800" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D800" s="2" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="801" spans="1:5">
+      <c r="A801" s="1">
+        <v>21002</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C801" s="1" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D801" s="1" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="802" spans="1:5">
+      <c r="A802" s="1">
+        <v>21003</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C802" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D802" s="1" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="803" spans="1:5" ht="27.75">
+      <c r="A803" s="1">
+        <v>21004</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C803" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D803" s="2" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="804" spans="1:5" ht="27.75">
+      <c r="A804" s="1">
+        <v>21005</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C804" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D804" s="2" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="805" spans="1:5" ht="27.75">
+      <c r="A805" s="1">
+        <v>21006</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C805" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D805" s="2" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="806" spans="1:5">
+      <c r="A806" s="1">
+        <v>21007</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C806" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D806" s="1" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="807" spans="1:5" ht="27.75">
+      <c r="A807" s="1">
+        <v>21008</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C807" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D807" s="2" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="808" spans="1:5">
+      <c r="A808" s="1">
+        <v>21009</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C808" s="1" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D808" s="1" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="809" spans="1:5" ht="27.75">
+      <c r="A809" s="1">
+        <v>21010</v>
+      </c>
+      <c r="B809" s="1" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C809" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D809" s="2" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="810" spans="1:5" ht="27.75">
+      <c r="A810" s="1">
+        <v>21011</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C810" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D810" s="2" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="811" spans="1:5" ht="27.75">
+      <c r="A811" s="1">
+        <v>21012</v>
+      </c>
+      <c r="B811" s="1" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C811" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D811" s="2" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="812" spans="1:5">
+      <c r="A812" s="1">
+        <v>21013</v>
+      </c>
+      <c r="B812" s="1" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C812" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D812" s="1" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E812" s="1" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="813" spans="1:5">
+      <c r="A813" s="1">
+        <v>21014</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C813" s="1" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D813" s="1" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="814" spans="1:5">
+      <c r="A814" s="1">
+        <v>21015</v>
+      </c>
+      <c r="B814" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C814" s="1" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D814" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E814" s="1" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="815" spans="1:5">
+      <c r="A815" s="1">
+        <v>21016</v>
+      </c>
+      <c r="B815" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C815" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D815" s="1" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="816" spans="1:5">
+      <c r="A816" s="1">
+        <v>21017</v>
+      </c>
+      <c r="B816" s="1" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C816" s="1" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D816" s="1" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="817" spans="2:5">
+      <c r="B817" s="1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C817" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D817" s="1" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="818" spans="2:5">
+      <c r="B818" s="1" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C818" s="1" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D818" s="1" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="819" spans="2:5">
+      <c r="B819" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C819" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D819" s="1" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="820" spans="2:5">
+      <c r="B820" s="1" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C820" s="1" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="821" spans="2:5">
+      <c r="B821" s="1" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C821" s="1" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="822" spans="2:5">
+      <c r="B822" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C822" s="1" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="823" spans="2:5">
+      <c r="B823" s="1" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C823" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D823" s="1" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="824" spans="2:5">
+      <c r="B824" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C824" s="1" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="825" spans="2:5">
+      <c r="B825" s="1" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C825" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E825" s="1" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="826" spans="2:5">
+      <c r="B826" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D826" s="1" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="827" spans="2:5">
+      <c r="B827" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="828" spans="2:5">
+      <c r="B828" s="1" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="829" spans="2:5">
+      <c r="B829" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D829" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E829" s="1" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="830" spans="2:5">
+      <c r="B830" s="1" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="831" spans="2:5">
+      <c r="B831" s="1" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="832" spans="2:5">
+      <c r="B832" s="1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C832" s="1" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D832" s="1" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="833" spans="2:4">
+      <c r="B833" s="1" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="834" spans="2:4">
+      <c r="B834" s="1" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D834" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="835" spans="2:4">
+      <c r="B835" s="1" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C835" s="1" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D835" s="1" t="s">
+        <v>2169</v>
       </c>
     </row>
   </sheetData>
@@ -18458,12 +20545,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BEDC60-BD86-4F0B-8906-B631C56865DE}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="15.9140625" customWidth="1"/>
-    <col min="5" max="5" width="52.4140625" customWidth="1"/>
+    <col min="3" max="3" width="18.73046875" customWidth="1"/>
+    <col min="4" max="4" width="15.9296875" customWidth="1"/>
+    <col min="5" max="5" width="52.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -18549,10 +20636,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E327196-0A94-422A-A422-84A769DDFF6A}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="2" max="3" width="16.08203125" customWidth="1"/>
-    <col min="5" max="5" width="31.83203125" customWidth="1"/>
+    <col min="2" max="3" width="16.06640625" customWidth="1"/>
+    <col min="5" max="5" width="31.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/词表.xlsx
+++ b/词表.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GRE\GRE-wordlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB0CEB0-828F-4DBB-97D8-2FCCC7C847DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65437EB-42A0-4394-AA16-D15BE70F30F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="quant" sheetId="3" r:id="rId3"/>
+    <sheet name="SE" sheetId="4" r:id="rId3"/>
+    <sheet name="quant" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="2170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="2187">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4543,14 +4544,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>urn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>n. 瓮（容器）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>quadrilateral</t>
   </si>
   <si>
@@ -5378,10 +5371,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>reconcile 调解 调和</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>placatory, mollifying</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8161,10 +8150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>savor, enjoy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>调味品</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8746,6 +8731,89 @@
   </si>
   <si>
     <t>dreadful, grave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numinous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 超自然的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>surrogate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. alternative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 阻碍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 诽谤, 诋毁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invariably</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 总是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vista</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 全景, 远景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suggests an expansive vista</t>
+  </si>
+  <si>
+    <t>reconcile 调解 调和 重归于好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>denigrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doleful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lugubrious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 悲伤的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opprobrium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>infamy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 名声狼藉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>savor, enjoy, delighted</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13747,6 +13815,9 @@
       <c r="C363" s="1" t="s">
         <v>847</v>
       </c>
+      <c r="D363" s="1" t="s">
+        <v>2179</v>
+      </c>
       <c r="E363" s="1" t="s">
         <v>875</v>
       </c>
@@ -14229,7 +14300,7 @@
         <v>925</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -14308,7 +14379,7 @@
         <v>936</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -15341,16 +15412,16 @@
         <v>13016</v>
       </c>
       <c r="B474" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C474" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="C474" s="1" t="s">
-        <v>1135</v>
-      </c>
       <c r="D474" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -15358,16 +15429,16 @@
         <v>13017</v>
       </c>
       <c r="B475" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D475" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="C475" s="1" t="s">
+      <c r="E475" s="1" t="s">
         <v>1138</v>
-      </c>
-      <c r="D475" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E475" s="1" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -15375,13 +15446,13 @@
         <v>13018</v>
       </c>
       <c r="B476" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D476" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D476" s="1" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -15389,13 +15460,13 @@
         <v>13019</v>
       </c>
       <c r="B477" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D477" s="1" t="s">
         <v>1144</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D477" s="1" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -15403,13 +15474,13 @@
         <v>13020</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -15417,13 +15488,13 @@
         <v>13021</v>
       </c>
       <c r="B479" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D479" s="1" t="s">
         <v>1149</v>
-      </c>
-      <c r="C479" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D479" s="1" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -15431,13 +15502,13 @@
         <v>13022</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -15445,16 +15516,16 @@
         <v>13023</v>
       </c>
       <c r="B481" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E481" s="1" t="s">
         <v>1154</v>
-      </c>
-      <c r="C481" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D481" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E481" s="1" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -15462,16 +15533,16 @@
         <v>13024</v>
       </c>
       <c r="B482" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E482" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="C482" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D482" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E482" s="1" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -15479,16 +15550,16 @@
         <v>13025</v>
       </c>
       <c r="B483" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D483" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="C483" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D483" s="1" t="s">
-        <v>1163</v>
-      </c>
       <c r="E483" s="1" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -15496,16 +15567,16 @@
         <v>13026</v>
       </c>
       <c r="B484" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E484" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="C484" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D484" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E484" s="1" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -15513,16 +15584,16 @@
         <v>13027</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -15530,13 +15601,13 @@
         <v>13028</v>
       </c>
       <c r="B486" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D486" s="1" t="s">
         <v>1169</v>
-      </c>
-      <c r="C486" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D486" s="1" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -15544,16 +15615,16 @@
         <v>13029</v>
       </c>
       <c r="B487" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D487" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="C487" s="1" t="s">
+      <c r="E487" s="1" t="s">
         <v>1173</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>1174</v>
-      </c>
-      <c r="E487" s="1" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="488" spans="1:5" ht="27.75">
@@ -15561,16 +15632,16 @@
         <v>13030</v>
       </c>
       <c r="B488" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C488" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D488" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="C488" s="2" t="s">
+      <c r="E488" s="1" t="s">
         <v>1177</v>
-      </c>
-      <c r="D488" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E488" s="1" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -15578,13 +15649,13 @@
         <v>13031</v>
       </c>
       <c r="B489" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D489" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D489" s="1" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -15592,13 +15663,13 @@
         <v>13032</v>
       </c>
       <c r="B490" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D490" s="1" t="s">
         <v>1183</v>
-      </c>
-      <c r="C490" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D490" s="1" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -15606,13 +15677,13 @@
         <v>13033</v>
       </c>
       <c r="B491" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C491" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="C491" s="1" t="s">
-        <v>1188</v>
-      </c>
       <c r="D491" s="1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -15620,13 +15691,13 @@
         <v>13034</v>
       </c>
       <c r="B492" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C492" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D492" s="1" t="s">
         <v>1189</v>
-      </c>
-      <c r="C492" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D492" s="1" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -15634,13 +15705,13 @@
         <v>13035</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -15648,13 +15719,13 @@
         <v>13036</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -15662,13 +15733,13 @@
         <v>13037</v>
       </c>
       <c r="B495" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D495" s="1" t="s">
         <v>1197</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D495" s="1" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -15676,13 +15747,13 @@
         <v>13038</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -15690,16 +15761,16 @@
         <v>13039</v>
       </c>
       <c r="B497" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C497" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D497" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="C497" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D497" s="1" t="s">
-        <v>1203</v>
-      </c>
       <c r="E497" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -15707,13 +15778,13 @@
         <v>13040</v>
       </c>
       <c r="B498" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C498" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D498" s="1" t="s">
         <v>1204</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D498" s="1" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -15721,13 +15792,13 @@
         <v>13041</v>
       </c>
       <c r="B499" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D499" s="1" t="s">
         <v>1207</v>
-      </c>
-      <c r="C499" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D499" s="1" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -15735,13 +15806,13 @@
         <v>13042</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -15749,13 +15820,13 @@
         <v>13043</v>
       </c>
       <c r="B501" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D501" s="1" t="s">
         <v>1211</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D501" s="1" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="502" spans="1:5" ht="27.75">
@@ -15763,13 +15834,13 @@
         <v>13044</v>
       </c>
       <c r="B502" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C502" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D502" s="2" t="s">
         <v>1214</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D502" s="2" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="503" spans="1:5">
@@ -15777,13 +15848,13 @@
         <v>13045</v>
       </c>
       <c r="B503" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D503" s="1" t="s">
         <v>1217</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D503" s="1" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="504" spans="1:5">
@@ -15791,13 +15862,13 @@
         <v>13046</v>
       </c>
       <c r="B504" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D504" s="1" t="s">
         <v>1220</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D504" s="1" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="505" spans="1:5">
@@ -15805,13 +15876,13 @@
         <v>13047</v>
       </c>
       <c r="B505" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D505" s="1" t="s">
         <v>1223</v>
-      </c>
-      <c r="C505" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D505" s="1" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -15819,13 +15890,13 @@
         <v>14001</v>
       </c>
       <c r="B506" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C506" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="C506" s="1" t="s">
-        <v>1228</v>
-      </c>
       <c r="D506" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="507" spans="1:5">
@@ -15833,13 +15904,13 @@
         <v>14002</v>
       </c>
       <c r="B507" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D507" s="1" t="s">
         <v>1229</v>
-      </c>
-      <c r="C507" s="1" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D507" s="1" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="508" spans="1:5">
@@ -15847,13 +15918,13 @@
         <v>14003</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -15861,13 +15932,13 @@
         <v>14004</v>
       </c>
       <c r="B509" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D509" s="1" t="s">
         <v>1233</v>
-      </c>
-      <c r="C509" s="1" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D509" s="1" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -15875,13 +15946,13 @@
         <v>14005</v>
       </c>
       <c r="B510" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D510" s="1" t="s">
         <v>1236</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D510" s="1" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -15889,13 +15960,13 @@
         <v>14006</v>
       </c>
       <c r="B511" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D511" s="1" t="s">
         <v>1239</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D511" s="1" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="512" spans="1:5">
@@ -15903,13 +15974,13 @@
         <v>14007</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="513" spans="1:5">
@@ -15917,13 +15988,13 @@
         <v>14008</v>
       </c>
       <c r="B513" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D513" s="1" t="s">
         <v>1244</v>
-      </c>
-      <c r="C513" s="1" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D513" s="1" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -15931,13 +16002,13 @@
         <v>14009</v>
       </c>
       <c r="B514" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D514" s="1" t="s">
         <v>1247</v>
-      </c>
-      <c r="C514" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D514" s="1" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="515" spans="1:5">
@@ -15945,13 +16016,13 @@
         <v>14010</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -15959,13 +16030,13 @@
         <v>14011</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="517" spans="1:5">
@@ -15973,13 +16044,13 @@
         <v>14012</v>
       </c>
       <c r="B517" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D517" s="1" t="s">
         <v>1253</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="518" spans="1:5">
@@ -15987,13 +16058,13 @@
         <v>14013</v>
       </c>
       <c r="B518" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D518" s="1" t="s">
         <v>1256</v>
-      </c>
-      <c r="C518" s="1" t="s">
-        <v>1257</v>
-      </c>
-      <c r="D518" s="1" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="519" spans="1:5">
@@ -16001,13 +16072,13 @@
         <v>14014</v>
       </c>
       <c r="B519" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D519" s="1" t="s">
         <v>1259</v>
-      </c>
-      <c r="C519" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="D519" s="1" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="520" spans="1:5">
@@ -16015,13 +16086,13 @@
         <v>14015</v>
       </c>
       <c r="B520" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D520" s="1" t="s">
         <v>1262</v>
-      </c>
-      <c r="C520" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D520" s="1" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="521" spans="1:5">
@@ -16029,13 +16100,13 @@
         <v>14016</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="522" spans="1:5">
@@ -16043,13 +16114,13 @@
         <v>14017</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="523" spans="1:5">
@@ -16057,13 +16128,13 @@
         <v>14018</v>
       </c>
       <c r="B523" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D523" s="1" t="s">
         <v>1269</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="D523" s="1" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="524" spans="1:5">
@@ -16071,13 +16142,13 @@
         <v>14019</v>
       </c>
       <c r="B524" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D524" s="1" t="s">
         <v>1272</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="D524" s="1" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="525" spans="1:5">
@@ -16085,13 +16156,13 @@
         <v>14020</v>
       </c>
       <c r="B525" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D525" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="C525" s="1" t="s">
-        <v>1276</v>
-      </c>
-      <c r="D525" s="1" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="526" spans="1:5">
@@ -16099,13 +16170,13 @@
         <v>14021</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="527" spans="1:5">
@@ -16113,13 +16184,13 @@
         <v>14022</v>
       </c>
       <c r="B527" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D527" s="1" t="s">
         <v>1280</v>
-      </c>
-      <c r="C527" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D527" s="1" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="528" spans="1:5">
@@ -16127,16 +16198,16 @@
         <v>14023</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="529" spans="1:5">
@@ -16144,13 +16215,13 @@
         <v>14024</v>
       </c>
       <c r="B529" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D529" s="1" t="s">
         <v>1285</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D529" s="1" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="530" spans="1:5">
@@ -16158,13 +16229,13 @@
         <v>14025</v>
       </c>
       <c r="B530" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D530" s="1" t="s">
         <v>1288</v>
-      </c>
-      <c r="C530" s="1" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D530" s="1" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="531" spans="1:5">
@@ -16172,13 +16243,13 @@
         <v>14026</v>
       </c>
       <c r="B531" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C531" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D531" s="1" t="s">
         <v>1291</v>
-      </c>
-      <c r="C531" s="1" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D531" s="1" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="532" spans="1:5">
@@ -16186,13 +16257,13 @@
         <v>14027</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="533" spans="1:5">
@@ -16200,13 +16271,13 @@
         <v>14028</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="534" spans="1:5">
@@ -16214,13 +16285,13 @@
         <v>14029</v>
       </c>
       <c r="B534" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D534" s="1" t="s">
         <v>1297</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D534" s="1" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="535" spans="1:5">
@@ -16228,13 +16299,13 @@
         <v>14030</v>
       </c>
       <c r="B535" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D535" s="1" t="s">
         <v>1300</v>
-      </c>
-      <c r="C535" s="1" t="s">
-        <v>1301</v>
-      </c>
-      <c r="D535" s="1" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="536" spans="1:5">
@@ -16242,13 +16313,13 @@
         <v>14031</v>
       </c>
       <c r="B536" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D536" s="1" t="s">
         <v>1303</v>
-      </c>
-      <c r="C536" s="1" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D536" s="1" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="537" spans="1:5">
@@ -16259,10 +16330,10 @@
         <v>323</v>
       </c>
       <c r="C537" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D537" s="1" t="s">
         <v>1304</v>
-      </c>
-      <c r="D537" s="1" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="538" spans="1:5">
@@ -16270,13 +16341,13 @@
         <v>14033</v>
       </c>
       <c r="B538" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C538" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D538" s="1" t="s">
         <v>1307</v>
-      </c>
-      <c r="C538" s="1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D538" s="1" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="539" spans="1:5">
@@ -16284,13 +16355,13 @@
         <v>14034</v>
       </c>
       <c r="B539" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C539" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D539" s="1" t="s">
         <v>1310</v>
-      </c>
-      <c r="C539" s="1" t="s">
-        <v>1311</v>
-      </c>
-      <c r="D539" s="1" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="540" spans="1:5">
@@ -16298,16 +16369,16 @@
         <v>14035</v>
       </c>
       <c r="B540" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D540" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="C540" s="1" t="s">
+      <c r="E540" s="1" t="s">
         <v>1314</v>
-      </c>
-      <c r="D540" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E540" s="1" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="541" spans="1:5">
@@ -16315,13 +16386,13 @@
         <v>14036</v>
       </c>
       <c r="B541" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D541" s="1" t="s">
         <v>1317</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D541" s="1" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="542" spans="1:5">
@@ -16329,13 +16400,13 @@
         <v>14037</v>
       </c>
       <c r="B542" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D542" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D542" s="1" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="543" spans="1:5">
@@ -16343,16 +16414,16 @@
         <v>14038</v>
       </c>
       <c r="B543" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D543" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="C543" s="1" t="s">
+      <c r="E543" s="1" t="s">
         <v>1324</v>
-      </c>
-      <c r="D543" s="1" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E543" s="1" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -16360,13 +16431,13 @@
         <v>14039</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="545" spans="1:5">
@@ -16374,13 +16445,13 @@
         <v>14040</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="546" spans="1:5">
@@ -16388,16 +16459,16 @@
         <v>14041</v>
       </c>
       <c r="B546" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D546" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="C546" s="1" t="s">
-        <v>1332</v>
-      </c>
-      <c r="D546" s="1" t="s">
-        <v>1334</v>
-      </c>
       <c r="E546" s="1" t="s">
-        <v>1333</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="547" spans="1:5">
@@ -16405,13 +16476,13 @@
         <v>14042</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -16419,13 +16490,13 @@
         <v>14043</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="549" spans="1:5">
@@ -16433,13 +16504,13 @@
         <v>14044</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="550" spans="1:5">
@@ -16447,13 +16518,13 @@
         <v>15001</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="551" spans="1:5">
@@ -16461,13 +16532,13 @@
         <v>15002</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="552" spans="1:5">
@@ -16475,16 +16546,16 @@
         <v>15003</v>
       </c>
       <c r="B552" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C552" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D552" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E552" s="1" t="s">
         <v>1349</v>
-      </c>
-      <c r="C552" s="1" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D552" s="1" t="s">
-        <v>1351</v>
-      </c>
-      <c r="E552" s="1" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="553" spans="1:5">
@@ -16492,16 +16563,16 @@
         <v>15004</v>
       </c>
       <c r="B553" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D553" s="1" t="s">
         <v>1353</v>
       </c>
-      <c r="C553" s="1" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D553" s="1" t="s">
-        <v>1356</v>
-      </c>
       <c r="E553" s="1" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="554" spans="1:5">
@@ -16509,13 +16580,13 @@
         <v>15005</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="555" spans="1:5">
@@ -16523,13 +16594,13 @@
         <v>15006</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="556" spans="1:5">
@@ -16537,16 +16608,16 @@
         <v>15007</v>
       </c>
       <c r="B556" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D556" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="C556" s="1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="D556" s="1" t="s">
-        <v>1364</v>
-      </c>
       <c r="E556" s="1" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -16554,13 +16625,13 @@
         <v>15008</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -16568,13 +16639,13 @@
         <v>15009</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="559" spans="1:5">
@@ -16582,13 +16653,13 @@
         <v>15010</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="C559" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D559" s="1" t="s">
         <v>1369</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -16596,16 +16667,16 @@
         <v>15011</v>
       </c>
       <c r="B560" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D560" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E560" s="1" t="s">
         <v>1373</v>
-      </c>
-      <c r="C560" s="1" t="s">
-        <v>1374</v>
-      </c>
-      <c r="D560" s="1" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E560" s="1" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -16613,16 +16684,16 @@
         <v>15012</v>
       </c>
       <c r="B561" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D561" s="1" t="s">
         <v>1375</v>
       </c>
-      <c r="C561" s="1" t="s">
-        <v>1374</v>
-      </c>
-      <c r="D561" s="1" t="s">
-        <v>1378</v>
-      </c>
       <c r="E561" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="562" spans="1:5">
@@ -16633,10 +16704,10 @@
         <v>223</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -16644,13 +16715,13 @@
         <v>15014</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -16658,13 +16729,13 @@
         <v>15015</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="565" spans="1:5">
@@ -16672,13 +16743,13 @@
         <v>15016</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="566" spans="1:5">
@@ -16686,13 +16757,13 @@
         <v>15017</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="567" spans="1:5">
@@ -16700,13 +16771,13 @@
         <v>15018</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -16717,10 +16788,10 @@
         <v>435</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -16728,13 +16799,13 @@
         <v>15020</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="570" spans="1:5">
@@ -16742,13 +16813,13 @@
         <v>15021</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="C570" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D570" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="D570" s="1" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="571" spans="1:5">
@@ -16756,16 +16827,16 @@
         <v>15022</v>
       </c>
       <c r="B571" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E571" s="1" t="s">
         <v>1400</v>
-      </c>
-      <c r="C571" s="1" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D571" s="1" t="s">
-        <v>1402</v>
-      </c>
-      <c r="E571" s="1" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -16773,13 +16844,13 @@
         <v>15023</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="573" spans="1:5">
@@ -16787,13 +16858,13 @@
         <v>15024</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -16801,13 +16872,13 @@
         <v>15025</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="575" spans="1:5">
@@ -16815,13 +16886,13 @@
         <v>15026</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="576" spans="1:5">
@@ -16829,13 +16900,13 @@
         <v>15027</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="577" spans="1:5">
@@ -16843,13 +16914,13 @@
         <v>15028</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="578" spans="1:5" ht="27.75">
@@ -16857,13 +16928,13 @@
         <v>15029</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -16871,13 +16942,13 @@
         <v>15030</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -16885,13 +16956,13 @@
         <v>15031</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="C580" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D580" s="1" t="s">
         <v>1419</v>
-      </c>
-      <c r="D580" s="1" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="581" spans="1:5">
@@ -16899,13 +16970,13 @@
         <v>15032</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="582" spans="1:5">
@@ -16913,13 +16984,13 @@
         <v>15033</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="583" spans="1:5">
@@ -16927,13 +16998,13 @@
         <v>15034</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="584" spans="1:5">
@@ -16941,13 +17012,13 @@
         <v>15035</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -16955,13 +17026,13 @@
         <v>15036</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="C585" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D585" s="1" t="s">
         <v>1431</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="586" spans="1:5">
@@ -16969,13 +17040,13 @@
         <v>15037</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -16983,16 +17054,16 @@
         <v>15038</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="E587" s="1" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -17000,13 +17071,13 @@
         <v>15039</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -17014,13 +17085,13 @@
         <v>15040</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="C589" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -17028,16 +17099,16 @@
         <v>15041</v>
       </c>
       <c r="B590" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D590" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E590" s="1" t="s">
         <v>1441</v>
-      </c>
-      <c r="C590" s="1" t="s">
-        <v>1431</v>
-      </c>
-      <c r="D590" s="1" t="s">
-        <v>1445</v>
-      </c>
-      <c r="E590" s="1" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -17045,13 +17116,13 @@
         <v>15042</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -17059,13 +17130,13 @@
         <v>15043</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="C592" s="1" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="593" spans="1:5">
@@ -17073,13 +17144,13 @@
         <v>15044</v>
       </c>
       <c r="B593" s="1" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="594" spans="1:5">
@@ -17087,13 +17158,13 @@
         <v>15045</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="C594" s="1" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="595" spans="1:5">
@@ -17101,16 +17172,16 @@
         <v>15046</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="C595" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E595" s="1" t="s">
         <v>1455</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E595" s="1" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="596" spans="1:5">
@@ -17118,13 +17189,13 @@
         <v>16001</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="C596" s="1" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -17132,13 +17203,13 @@
         <v>16002</v>
       </c>
       <c r="B597" s="1" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="598" spans="1:5">
@@ -17146,13 +17217,13 @@
         <v>16003</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="599" spans="1:5">
@@ -17160,13 +17231,13 @@
         <v>16004</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="C599" s="1" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="600" spans="1:5">
@@ -17174,13 +17245,13 @@
         <v>16005</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="601" spans="1:5">
@@ -17188,13 +17259,13 @@
         <v>16006</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="C601" s="1" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="602" spans="1:5">
@@ -17202,13 +17273,13 @@
         <v>16007</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="C602" s="1" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="603" spans="1:5">
@@ -17216,13 +17287,13 @@
         <v>16008</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="C603" s="1" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -17230,13 +17301,13 @@
         <v>16009</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="C604" s="1" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="605" spans="1:5">
@@ -17244,13 +17315,13 @@
         <v>16010</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -17258,13 +17329,13 @@
         <v>16011</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="607" spans="1:5">
@@ -17272,13 +17343,13 @@
         <v>16012</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="C607" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D607" s="1" t="s">
         <v>1486</v>
-      </c>
-      <c r="D607" s="1" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="608" spans="1:5">
@@ -17286,13 +17357,13 @@
         <v>16013</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="609" spans="1:5">
@@ -17300,13 +17371,13 @@
         <v>16014</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="C609" s="1" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="610" spans="1:5">
@@ -17314,13 +17385,13 @@
         <v>16015</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="C610" s="1" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="611" spans="1:5">
@@ -17328,13 +17399,13 @@
         <v>16016</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="612" spans="1:5">
@@ -17342,13 +17413,13 @@
         <v>16017</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="C612" s="1" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="613" spans="1:5">
@@ -17356,13 +17427,13 @@
         <v>16018</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="C613" s="1" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="614" spans="1:5">
@@ -17370,13 +17441,13 @@
         <v>16019</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="C614" s="1" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="615" spans="1:5">
@@ -17384,13 +17455,13 @@
         <v>16020</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="C615" s="1" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="616" spans="1:5">
@@ -17398,13 +17469,13 @@
         <v>16021</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="C616" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D616" s="1" t="s">
         <v>1505</v>
-      </c>
-      <c r="D616" s="1" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="617" spans="1:5">
@@ -17412,16 +17483,16 @@
         <v>16022</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="C617" s="1" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="618" spans="1:5">
@@ -17429,13 +17500,13 @@
         <v>16023</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="C618" s="1" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -17443,13 +17514,13 @@
         <v>16024</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="C619" s="1" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -17457,13 +17528,13 @@
         <v>16025</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="C620" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D620" s="1" t="s">
         <v>1516</v>
-      </c>
-      <c r="D620" s="1" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -17471,13 +17542,13 @@
         <v>16026</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="C621" s="1" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -17485,13 +17556,13 @@
         <v>16027</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="C622" s="1" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="623" spans="1:5">
@@ -17499,13 +17570,13 @@
         <v>16028</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="C623" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D623" s="1" t="s">
         <v>1523</v>
-      </c>
-      <c r="D623" s="1" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -17513,16 +17584,16 @@
         <v>16029</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="C624" s="1" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -17530,13 +17601,13 @@
         <v>16030</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="C625" s="1" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -17544,13 +17615,13 @@
         <v>16031</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="C626" s="1" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -17558,13 +17629,13 @@
         <v>16032</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="C627" s="1" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -17572,13 +17643,13 @@
         <v>16033</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="C628" s="1" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -17586,13 +17657,13 @@
         <v>16034</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="C629" s="1" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="630" spans="1:5">
@@ -17600,13 +17671,13 @@
         <v>16035</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="C630" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -17614,13 +17685,13 @@
         <v>16036</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="C631" s="1" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -17628,13 +17699,13 @@
         <v>16037</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="C632" s="1" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="633" spans="1:5">
@@ -17642,16 +17713,16 @@
         <v>16038</v>
       </c>
       <c r="B633" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D633" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="C633" s="1" t="s">
-        <v>1555</v>
-      </c>
-      <c r="D633" s="1" t="s">
-        <v>1557</v>
-      </c>
       <c r="E633" s="1" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -17659,13 +17730,13 @@
         <v>16039</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="C634" s="1" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -17673,13 +17744,13 @@
         <v>16040</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="C635" s="1" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -17687,13 +17758,13 @@
         <v>16041</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -17701,13 +17772,13 @@
         <v>17001</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="C637" s="1" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -17715,16 +17786,16 @@
         <v>17002</v>
       </c>
       <c r="B638" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E638" s="1" t="s">
         <v>1569</v>
-      </c>
-      <c r="C638" s="1" t="s">
-        <v>1570</v>
-      </c>
-      <c r="D638" s="1" t="s">
-        <v>1571</v>
-      </c>
-      <c r="E638" s="1" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -17732,16 +17803,16 @@
         <v>17003</v>
       </c>
       <c r="B639" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E639" s="1" t="s">
         <v>1573</v>
-      </c>
-      <c r="C639" s="1" t="s">
-        <v>1574</v>
-      </c>
-      <c r="D639" s="1" t="s">
-        <v>1575</v>
-      </c>
-      <c r="E639" s="1" t="s">
-        <v>1576</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -17749,16 +17820,16 @@
         <v>17004</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="641" spans="1:5">
@@ -17766,13 +17837,13 @@
         <v>17005</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -17780,13 +17851,13 @@
         <v>17006</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="643" spans="1:5">
@@ -17794,13 +17865,13 @@
         <v>17007</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -17808,16 +17879,16 @@
         <v>17008</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="C644" s="1" t="s">
         <v>600</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="645" spans="1:5">
@@ -17825,16 +17896,16 @@
         <v>17009</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="C645" s="1" t="s">
         <v>600</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="646" spans="1:5">
@@ -17842,16 +17913,16 @@
         <v>17010</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="C646" s="1" t="s">
         <v>600</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="647" spans="1:5">
@@ -17859,16 +17930,16 @@
         <v>17011</v>
       </c>
       <c r="B647" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E647" s="1" t="s">
         <v>1607</v>
-      </c>
-      <c r="C647" s="1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="D647" s="1" t="s">
-        <v>1609</v>
-      </c>
-      <c r="E647" s="1" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -17876,13 +17947,13 @@
         <v>17012</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="649" spans="1:5">
@@ -17890,16 +17961,16 @@
         <v>17013</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="C649" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D649" s="1" t="s">
         <v>1612</v>
       </c>
-      <c r="D649" s="1" t="s">
-        <v>1615</v>
-      </c>
       <c r="E649" s="1" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="650" spans="1:5">
@@ -17907,13 +17978,13 @@
         <v>17014</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="651" spans="1:5">
@@ -17921,10 +17992,10 @@
         <v>17015</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="D651" s="1" t="s">
         <v>564</v>
@@ -17935,13 +18006,13 @@
         <v>17016</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -17949,13 +18020,13 @@
         <v>17017</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="654" spans="1:5">
@@ -17963,13 +18034,13 @@
         <v>17018</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -17977,13 +18048,13 @@
         <v>17019</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="656" spans="1:5">
@@ -17991,16 +18062,16 @@
         <v>17020</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="C656" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E656" s="1" t="s">
         <v>1631</v>
-      </c>
-      <c r="D656" s="1" t="s">
-        <v>1633</v>
-      </c>
-      <c r="E656" s="1" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -18011,13 +18082,13 @@
         <v>384</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -18025,13 +18096,13 @@
         <v>17022</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="C658" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D658" s="1" t="s">
         <v>1635</v>
-      </c>
-      <c r="D658" s="1" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -18039,13 +18110,13 @@
         <v>17023</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="660" spans="1:5">
@@ -18053,13 +18124,13 @@
         <v>17024</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -18067,16 +18138,16 @@
         <v>17025</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C661" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D661" s="1" t="s">
         <v>1645</v>
       </c>
-      <c r="C661" s="1" t="s">
-        <v>1646</v>
-      </c>
-      <c r="D661" s="1" t="s">
-        <v>1648</v>
-      </c>
       <c r="E661" s="1" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="662" spans="1:5">
@@ -18084,13 +18155,13 @@
         <v>17026</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="663" spans="1:5">
@@ -18098,16 +18169,16 @@
         <v>17027</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C663" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D663" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="C663" s="1" t="s">
-        <v>1652</v>
-      </c>
-      <c r="D663" s="1" t="s">
-        <v>1654</v>
-      </c>
       <c r="E663" s="1" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -18115,13 +18186,13 @@
         <v>17028</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -18129,13 +18200,13 @@
         <v>17029</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -18143,13 +18214,13 @@
         <v>17030</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="667" spans="1:5">
@@ -18157,13 +18228,13 @@
         <v>17031</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -18171,13 +18242,13 @@
         <v>17032</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -18185,16 +18256,16 @@
         <v>17033</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E669" s="1" t="s">
         <v>1669</v>
-      </c>
-      <c r="C669" s="1" t="s">
-        <v>1670</v>
-      </c>
-      <c r="D669" s="1" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E669" s="1" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="670" spans="1:5">
@@ -18202,13 +18273,13 @@
         <v>17034</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="C670" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D670" s="1" t="s">
         <v>1670</v>
-      </c>
-      <c r="D670" s="1" t="s">
-        <v>1673</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -18216,13 +18287,13 @@
         <v>17035</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="672" spans="1:5">
@@ -18233,10 +18304,10 @@
         <v>747</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -18244,13 +18315,13 @@
         <v>17037</v>
       </c>
       <c r="B673" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C673" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D673" s="1" t="s">
         <v>1678</v>
-      </c>
-      <c r="C673" s="1" t="s">
-        <v>1679</v>
-      </c>
-      <c r="D673" s="1" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="674" spans="1:5">
@@ -18258,16 +18329,16 @@
         <v>17038</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="675" spans="1:5">
@@ -18275,16 +18346,16 @@
         <v>17039</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="676" spans="1:5">
@@ -18292,13 +18363,13 @@
         <v>17040</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="677" spans="1:5">
@@ -18306,13 +18377,13 @@
         <v>17041</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="678" spans="1:5">
@@ -18320,13 +18391,13 @@
         <v>17042</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="679" spans="1:5" ht="27.75">
@@ -18334,13 +18405,13 @@
         <v>17043</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="C679" s="2" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="680" spans="1:5">
@@ -18348,13 +18419,13 @@
         <v>17044</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="681" spans="1:5">
@@ -18362,13 +18433,13 @@
         <v>17045</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="682" spans="1:5">
@@ -18376,13 +18447,13 @@
         <v>17046</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>481</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="683" spans="1:5">
@@ -18390,16 +18461,16 @@
         <v>18001</v>
       </c>
       <c r="B683" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D683" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E683" s="1" t="s">
         <v>1707</v>
-      </c>
-      <c r="C683" s="1" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D683" s="1" t="s">
-        <v>1709</v>
-      </c>
-      <c r="E683" s="1" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="684" spans="1:5">
@@ -18407,13 +18478,13 @@
         <v>18002</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="685" spans="1:5">
@@ -18421,13 +18492,13 @@
         <v>18003</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="686" spans="1:5">
@@ -18435,13 +18506,13 @@
         <v>18004</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="687" spans="1:5">
@@ -18449,13 +18520,13 @@
         <v>18005</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="688" spans="1:5">
@@ -18463,16 +18534,16 @@
         <v>18006</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="D688" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E688" s="1" t="s">
         <v>1719</v>
-      </c>
-      <c r="E688" s="1" t="s">
-        <v>1722</v>
       </c>
     </row>
     <row r="689" spans="1:5">
@@ -18480,13 +18551,13 @@
         <v>18007</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="690" spans="1:5">
@@ -18494,13 +18565,13 @@
         <v>18008</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="691" spans="1:5">
@@ -18508,16 +18579,16 @@
         <v>18009</v>
       </c>
       <c r="B691" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D691" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E691" s="1" t="s">
         <v>1729</v>
-      </c>
-      <c r="C691" s="1" t="s">
-        <v>1730</v>
-      </c>
-      <c r="D691" s="1" t="s">
-        <v>1731</v>
-      </c>
-      <c r="E691" s="1" t="s">
-        <v>1732</v>
       </c>
     </row>
     <row r="692" spans="1:5">
@@ -18525,16 +18596,16 @@
         <v>18010</v>
       </c>
       <c r="B692" s="1" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="E692" s="1" t="s">
         <v>1733</v>
-      </c>
-      <c r="C692" s="1" t="s">
-        <v>1734</v>
-      </c>
-      <c r="D692" s="1" t="s">
-        <v>1735</v>
-      </c>
-      <c r="E692" s="1" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="693" spans="1:5">
@@ -18542,13 +18613,13 @@
         <v>18011</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="D693" s="1" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="694" spans="1:5">
@@ -18556,13 +18627,13 @@
         <v>18012</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="D694" s="1" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="695" spans="1:5">
@@ -18570,13 +18641,13 @@
         <v>18013</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="D695" s="1" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="696" spans="1:5">
@@ -18587,10 +18658,10 @@
         <v>114</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
       <c r="D696" s="1" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="697" spans="1:5">
@@ -18598,13 +18669,13 @@
         <v>18015</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
       <c r="C697" s="1" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
       <c r="D697" s="1" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="698" spans="1:5">
@@ -18612,13 +18683,13 @@
         <v>18016</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="C698" s="1" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="D698" s="1" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="699" spans="1:5">
@@ -18626,16 +18697,16 @@
         <v>18017</v>
       </c>
       <c r="B699" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E699" s="1" t="s">
         <v>1754</v>
-      </c>
-      <c r="C699" s="1" t="s">
-        <v>1755</v>
-      </c>
-      <c r="D699" s="1" t="s">
-        <v>1756</v>
-      </c>
-      <c r="E699" s="1" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="700" spans="1:5">
@@ -18643,13 +18714,13 @@
         <v>18018</v>
       </c>
       <c r="B700" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D700" s="1" t="s">
         <v>1756</v>
-      </c>
-      <c r="C700" s="1" t="s">
-        <v>1758</v>
-      </c>
-      <c r="D700" s="1" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="701" spans="1:5">
@@ -18657,13 +18728,13 @@
         <v>18019</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
       <c r="C701" s="1" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
       <c r="D701" s="1" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="702" spans="1:5">
@@ -18671,13 +18742,13 @@
         <v>18020</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
       <c r="C702" s="1" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D702" s="1" t="s">
         <v>1761</v>
-      </c>
-      <c r="D702" s="1" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="703" spans="1:5">
@@ -18685,13 +18756,13 @@
         <v>18021</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="C703" s="1" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="D703" s="1" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="704" spans="1:5">
@@ -18699,13 +18770,13 @@
         <v>18022</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="C704" s="1" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="D704" s="1" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -18713,13 +18784,13 @@
         <v>18023</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="C705" s="1" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="D705" s="1" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -18727,13 +18798,13 @@
         <v>18024</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="C706" s="1" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D706" s="1" t="s">
         <v>1772</v>
-      </c>
-      <c r="D706" s="1" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -18741,13 +18812,13 @@
         <v>18025</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="C707" s="1" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="D707" s="1" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -18755,13 +18826,13 @@
         <v>18026</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
       <c r="C708" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D708" s="1" t="s">
         <v>1777</v>
-      </c>
-      <c r="D708" s="1" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -18769,13 +18840,13 @@
         <v>18027</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="C709" s="1" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="D709" s="1" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -18783,13 +18854,13 @@
         <v>18028</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
       <c r="C710" s="1" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="D710" s="1" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -18797,13 +18868,13 @@
         <v>18029</v>
       </c>
       <c r="B711" s="1" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="C711" s="1" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="D711" s="1" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -18811,13 +18882,13 @@
         <v>18030</v>
       </c>
       <c r="B712" s="1" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="C712" s="1" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="D712" s="1" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="713" spans="1:4" ht="27.75">
@@ -18825,10 +18896,10 @@
         <v>18031</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -18836,13 +18907,13 @@
         <v>18032</v>
       </c>
       <c r="B714" s="1" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
       <c r="C714" s="1" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="D714" s="1" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -18850,13 +18921,13 @@
         <v>18033</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="C715" s="1" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
       <c r="D715" s="1" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -18864,13 +18935,13 @@
         <v>18034</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
       <c r="C716" s="1" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="D716" s="1" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -18878,13 +18949,13 @@
         <v>18035</v>
       </c>
       <c r="B717" s="1" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
       <c r="C717" s="1" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="D717" s="1" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -18892,13 +18963,13 @@
         <v>18036</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="C718" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D718" s="1" t="s">
         <v>1802</v>
-      </c>
-      <c r="D718" s="1" t="s">
-        <v>1805</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -18906,13 +18977,13 @@
         <v>18037</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="C719" s="1" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="D719" s="1" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -18920,13 +18991,13 @@
         <v>18038</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="C720" s="1" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="D720" s="1" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="721" spans="1:5">
@@ -18934,16 +19005,16 @@
         <v>18039</v>
       </c>
       <c r="B721" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C721" s="1" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D721" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E721" s="1" t="s">
         <v>1812</v>
-      </c>
-      <c r="C721" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="D721" s="1" t="s">
-        <v>1814</v>
-      </c>
-      <c r="E721" s="1" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="722" spans="1:5">
@@ -18951,13 +19022,13 @@
         <v>18040</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="C722" s="1" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="D722" s="1" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="723" spans="1:5">
@@ -18965,13 +19036,13 @@
         <v>18041</v>
       </c>
       <c r="B723" s="1" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="C723" s="1" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
       <c r="D723" s="1" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="724" spans="1:5">
@@ -18979,13 +19050,13 @@
         <v>19001</v>
       </c>
       <c r="B724" s="1" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="C724" s="1" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
       <c r="D724" s="1" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="725" spans="1:5">
@@ -18993,13 +19064,13 @@
         <v>19002</v>
       </c>
       <c r="B725" s="1" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="C725" s="1" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="D725" s="1" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="726" spans="1:5">
@@ -19007,13 +19078,13 @@
         <v>19003</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
       <c r="C726" s="1" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
       <c r="D726" s="1" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="727" spans="1:5">
@@ -19021,13 +19092,13 @@
         <v>19004</v>
       </c>
       <c r="B727" s="1" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
       <c r="C727" s="1" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="D727" s="1" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="728" spans="1:5">
@@ -19035,13 +19106,13 @@
         <v>19005</v>
       </c>
       <c r="B728" s="1" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="C728" s="1" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="D728" s="1" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="729" spans="1:5">
@@ -19049,13 +19120,13 @@
         <v>19006</v>
       </c>
       <c r="B729" s="1" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="C729" s="1" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="D729" s="1" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -19063,13 +19134,13 @@
         <v>19007</v>
       </c>
       <c r="B730" s="1" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
       <c r="C730" s="1" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="D730" s="1" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="731" spans="1:5">
@@ -19077,16 +19148,16 @@
         <v>19008</v>
       </c>
       <c r="B731" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C731" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D731" s="1" t="s">
         <v>1845</v>
       </c>
-      <c r="C731" s="1" t="s">
-        <v>1846</v>
-      </c>
-      <c r="D731" s="1" t="s">
-        <v>1848</v>
-      </c>
       <c r="E731" s="1" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="732" spans="1:5">
@@ -19094,13 +19165,13 @@
         <v>19009</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="C732" s="1" t="s">
-        <v>1850</v>
+        <v>1847</v>
       </c>
       <c r="E732" s="1" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="733" spans="1:5">
@@ -19108,13 +19179,13 @@
         <v>19010</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
       <c r="C733" s="1" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
       <c r="D733" s="1" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="734" spans="1:5">
@@ -19122,13 +19193,13 @@
         <v>19011</v>
       </c>
       <c r="B734" s="1" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="C734" s="1" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
       <c r="D734" s="1" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="735" spans="1:5">
@@ -19136,16 +19207,16 @@
         <v>19012</v>
       </c>
       <c r="B735" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C735" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D735" s="1" t="s">
         <v>1858</v>
       </c>
-      <c r="C735" s="1" t="s">
-        <v>1859</v>
-      </c>
-      <c r="D735" s="1" t="s">
-        <v>1861</v>
-      </c>
       <c r="E735" s="1" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="736" spans="1:5">
@@ -19153,13 +19224,13 @@
         <v>19013</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
       <c r="C736" s="1" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
       <c r="D736" s="1" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="737" spans="1:5">
@@ -19167,13 +19238,13 @@
         <v>19014</v>
       </c>
       <c r="B737" s="1" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="C737" s="1" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="D737" s="1" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="738" spans="1:5">
@@ -19181,13 +19252,13 @@
         <v>19015</v>
       </c>
       <c r="B738" s="1" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="C738" s="1" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="D738" s="1" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="739" spans="1:5">
@@ -19195,13 +19266,13 @@
         <v>19016</v>
       </c>
       <c r="B739" s="1" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="C739" s="1" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="D739" s="1" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="740" spans="1:5" ht="27.75">
@@ -19209,13 +19280,13 @@
         <v>19017</v>
       </c>
       <c r="B740" s="1" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="D740" s="2" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="741" spans="1:5">
@@ -19223,13 +19294,13 @@
         <v>19018</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
       <c r="C741" s="1" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="D741" s="1" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="742" spans="1:5">
@@ -19237,13 +19308,13 @@
         <v>19019</v>
       </c>
       <c r="B742" s="1" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
       <c r="C742" s="1" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
       <c r="D742" s="1" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="743" spans="1:5">
@@ -19251,13 +19322,13 @@
         <v>19020</v>
       </c>
       <c r="B743" s="1" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
       <c r="C743" s="1" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="D743" s="1" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="744" spans="1:5">
@@ -19265,13 +19336,13 @@
         <v>19021</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="C744" s="1" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="D744" s="1" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="745" spans="1:5" ht="27.75">
@@ -19279,13 +19350,13 @@
         <v>19022</v>
       </c>
       <c r="B745" s="1" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
       <c r="D745" s="2" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="746" spans="1:5">
@@ -19293,13 +19364,13 @@
         <v>19023</v>
       </c>
       <c r="B746" s="1" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="C746" s="1" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="D746" s="1" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="747" spans="1:5">
@@ -19307,13 +19378,13 @@
         <v>19024</v>
       </c>
       <c r="B747" s="1" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="C747" s="1" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="D747" s="1" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="748" spans="1:5">
@@ -19324,10 +19395,10 @@
         <v>59</v>
       </c>
       <c r="C748" s="1" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="D748" s="1" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="749" spans="1:5">
@@ -19335,13 +19406,13 @@
         <v>19026</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="C749" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D749" s="1" t="s">
         <v>1898</v>
-      </c>
-      <c r="D749" s="1" t="s">
-        <v>1901</v>
       </c>
     </row>
     <row r="750" spans="1:5">
@@ -19349,16 +19420,16 @@
         <v>19027</v>
       </c>
       <c r="B750" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C750" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D750" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E750" s="1" t="s">
         <v>1902</v>
-      </c>
-      <c r="C750" s="1" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D750" s="1" t="s">
-        <v>1904</v>
-      </c>
-      <c r="E750" s="1" t="s">
-        <v>1905</v>
       </c>
     </row>
     <row r="751" spans="1:5">
@@ -19366,16 +19437,16 @@
         <v>19028</v>
       </c>
       <c r="B751" s="1" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="C751" s="1" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
       <c r="D751" s="1" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
       <c r="E751" s="1" t="s">
-        <v>1907</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="752" spans="1:5">
@@ -19383,13 +19454,13 @@
         <v>19029</v>
       </c>
       <c r="B752" s="1" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
       <c r="C752" s="1" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="D752" s="1" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="753" spans="1:5">
@@ -19397,13 +19468,13 @@
         <v>19030</v>
       </c>
       <c r="B753" s="1" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
       <c r="C753" s="1" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="D753" s="1" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="754" spans="1:5">
@@ -19411,13 +19482,13 @@
         <v>19031</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
       <c r="C754" s="1" t="s">
+        <v>1910</v>
+      </c>
+      <c r="D754" s="1" t="s">
         <v>1913</v>
-      </c>
-      <c r="D754" s="1" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="755" spans="1:5">
@@ -19425,13 +19496,13 @@
         <v>19032</v>
       </c>
       <c r="B755" s="1" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="C755" s="1" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="D755" s="1" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="756" spans="1:5">
@@ -19439,13 +19510,13 @@
         <v>19033</v>
       </c>
       <c r="B756" s="1" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="C756" s="1" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="D756" s="1" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="757" spans="1:5">
@@ -19453,16 +19524,16 @@
         <v>20001</v>
       </c>
       <c r="B757" s="1" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C757" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E757" s="1" t="s">
         <v>1923</v>
-      </c>
-      <c r="C757" s="1" t="s">
-        <v>1924</v>
-      </c>
-      <c r="D757" s="1" t="s">
-        <v>1925</v>
-      </c>
-      <c r="E757" s="1" t="s">
-        <v>1926</v>
       </c>
     </row>
     <row r="758" spans="1:5">
@@ -19470,13 +19541,13 @@
         <v>20002</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="C758" s="1" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="D758" s="1" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="759" spans="1:5">
@@ -19484,13 +19555,13 @@
         <v>20003</v>
       </c>
       <c r="B759" s="1" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="C759" s="1" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="D759" s="1" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="760" spans="1:5">
@@ -19498,13 +19569,13 @@
         <v>20004</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="C760" s="1" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="D760" s="1" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="761" spans="1:5">
@@ -19512,13 +19583,13 @@
         <v>20005</v>
       </c>
       <c r="B761" s="1" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="C761" s="1" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
       <c r="D761" s="1" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="762" spans="1:5">
@@ -19526,13 +19597,13 @@
         <v>20006</v>
       </c>
       <c r="B762" s="1" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="C762" s="1" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="D762" s="1" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="763" spans="1:5">
@@ -19540,13 +19611,13 @@
         <v>20007</v>
       </c>
       <c r="B763" s="1" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="C763" s="1" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="D763" s="1" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="764" spans="1:5">
@@ -19554,13 +19625,13 @@
         <v>20008</v>
       </c>
       <c r="B764" s="1" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
       <c r="C764" s="1" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="D764" s="1" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="765" spans="1:5">
@@ -19568,13 +19639,13 @@
         <v>20009</v>
       </c>
       <c r="B765" s="1" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
       <c r="C765" s="1" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="D765" s="1" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="766" spans="1:5">
@@ -19582,16 +19653,16 @@
         <v>20010</v>
       </c>
       <c r="B766" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C766" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E766" s="1" t="s">
         <v>1951</v>
-      </c>
-      <c r="C766" s="1" t="s">
-        <v>1952</v>
-      </c>
-      <c r="D766" s="1" t="s">
-        <v>1953</v>
-      </c>
-      <c r="E766" s="1" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="767" spans="1:5">
@@ -19599,13 +19670,13 @@
         <v>20011</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="C767" s="1" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="D767" s="1" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="768" spans="1:5">
@@ -19613,13 +19684,13 @@
         <v>20012</v>
       </c>
       <c r="B768" s="1" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="C768" s="1" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="D768" s="1" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="769" spans="1:5">
@@ -19627,13 +19698,13 @@
         <v>20013</v>
       </c>
       <c r="B769" s="1" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="C769" s="1" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
       <c r="D769" s="1" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="770" spans="1:5">
@@ -19641,13 +19712,13 @@
         <v>20014</v>
       </c>
       <c r="B770" s="1" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="C770" s="1" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="D770" s="1" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="771" spans="1:5">
@@ -19655,13 +19726,13 @@
         <v>20015</v>
       </c>
       <c r="B771" s="1" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="C771" s="1" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="D771" s="1" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="772" spans="1:5">
@@ -19669,13 +19740,13 @@
         <v>20016</v>
       </c>
       <c r="B772" s="1" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="C772" s="1" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="D772" s="1" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="773" spans="1:5">
@@ -19683,13 +19754,13 @@
         <v>20017</v>
       </c>
       <c r="B773" s="1" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="C773" s="1" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="D773" s="1" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="774" spans="1:5">
@@ -19697,13 +19768,13 @@
         <v>20018</v>
       </c>
       <c r="B774" s="1" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="C774" s="1" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="D774" s="1" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="775" spans="1:5">
@@ -19711,16 +19782,16 @@
         <v>20019</v>
       </c>
       <c r="B775" s="1" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C775" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D775" s="1" t="s">
         <v>1979</v>
       </c>
-      <c r="C775" s="1" t="s">
-        <v>1980</v>
-      </c>
-      <c r="D775" s="1" t="s">
-        <v>1982</v>
-      </c>
       <c r="E775" s="1" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="776" spans="1:5">
@@ -19728,16 +19799,16 @@
         <v>20020</v>
       </c>
       <c r="B776" s="1" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E776" s="1" t="s">
         <v>1983</v>
-      </c>
-      <c r="C776" s="1" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D776" s="1" t="s">
-        <v>1985</v>
-      </c>
-      <c r="E776" s="1" t="s">
-        <v>1986</v>
       </c>
     </row>
     <row r="777" spans="1:5">
@@ -19745,13 +19816,13 @@
         <v>20021</v>
       </c>
       <c r="B777" s="1" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="C777" s="1" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="D777" s="1" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="778" spans="1:5">
@@ -19759,13 +19830,13 @@
         <v>20022</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="C778" s="1" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="D778" s="1" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="779" spans="1:5">
@@ -19773,13 +19844,13 @@
         <v>20023</v>
       </c>
       <c r="B779" s="1" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="C779" s="1" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="D779" s="1" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="780" spans="1:5">
@@ -19787,13 +19858,13 @@
         <v>20024</v>
       </c>
       <c r="B780" s="1" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="C780" s="1" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="D780" s="1" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="781" spans="1:5">
@@ -19801,16 +19872,16 @@
         <v>20025</v>
       </c>
       <c r="B781" s="1" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D781" s="1" t="s">
         <v>1999</v>
       </c>
-      <c r="C781" s="1" t="s">
-        <v>2000</v>
-      </c>
-      <c r="D781" s="1" t="s">
-        <v>2002</v>
-      </c>
       <c r="E781" s="1" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="782" spans="1:5">
@@ -19818,16 +19889,16 @@
         <v>20026</v>
       </c>
       <c r="B782" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D782" s="1" t="s">
         <v>2003</v>
       </c>
-      <c r="C782" s="1" t="s">
-        <v>2004</v>
-      </c>
-      <c r="D782" s="1" t="s">
-        <v>2006</v>
-      </c>
       <c r="E782" s="1" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="783" spans="1:5">
@@ -19835,13 +19906,13 @@
         <v>20027</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="C783" s="1" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D783" s="1" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="784" spans="1:5">
@@ -19852,13 +19923,13 @@
         <v>249</v>
       </c>
       <c r="C784" s="1" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D784" s="1" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E784" s="1" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="785" spans="1:5">
@@ -19866,13 +19937,13 @@
         <v>20029</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C785" s="1" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="D785" s="1" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="786" spans="1:5">
@@ -19880,13 +19951,13 @@
         <v>20030</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C786" s="1" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D786" s="1" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="787" spans="1:5">
@@ -19894,13 +19965,13 @@
         <v>20031</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C787" s="1" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D787" s="1" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="788" spans="1:5">
@@ -19908,13 +19979,13 @@
         <v>20032</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C788" s="1" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D788" s="1" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="789" spans="1:5">
@@ -19922,16 +19993,16 @@
         <v>20033</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C789" s="1" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D789" s="1" t="s">
-        <v>2027</v>
+        <v>2186</v>
       </c>
       <c r="E789" s="1" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="790" spans="1:5">
@@ -19939,13 +20010,13 @@
         <v>20034</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="C790" s="1" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="D790" s="1" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="791" spans="1:5">
@@ -19953,13 +20024,13 @@
         <v>20035</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="C791" s="1" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="D791" s="1" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="792" spans="1:5">
@@ -19967,13 +20038,13 @@
         <v>20036</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="C792" s="1" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="D792" s="1" t="s">
-        <v>2037</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="793" spans="1:5">
@@ -19981,13 +20052,13 @@
         <v>20037</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>2038</v>
+        <v>2034</v>
       </c>
       <c r="C793" s="1" t="s">
-        <v>2039</v>
+        <v>2035</v>
       </c>
       <c r="D793" s="1" t="s">
-        <v>2040</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="794" spans="1:5">
@@ -19995,13 +20066,13 @@
         <v>20038</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="C794" s="1" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="D794" s="1" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="795" spans="1:5">
@@ -20009,13 +20080,13 @@
         <v>20039</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="C795" s="1" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="D795" s="1" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="796" spans="1:5">
@@ -20023,16 +20094,16 @@
         <v>20040</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="C796" s="1" t="s">
-        <v>2048</v>
+        <v>2044</v>
       </c>
       <c r="D796" s="1" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="E796" s="1" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="797" spans="1:5">
@@ -20040,13 +20111,13 @@
         <v>20041</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="C797" s="1" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="D797" s="1" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="798" spans="1:5">
@@ -20054,13 +20125,13 @@
         <v>20042</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>2054</v>
+        <v>2050</v>
       </c>
       <c r="C798" s="1" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
       <c r="D798" s="1" t="s">
-        <v>2056</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="799" spans="1:5">
@@ -20068,13 +20139,13 @@
         <v>20043</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>2057</v>
+        <v>2053</v>
       </c>
       <c r="C799" s="1" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="D799" s="1" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="800" spans="1:5" ht="27.75">
@@ -20082,13 +20153,13 @@
         <v>21001</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="D800" s="2" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="801" spans="1:5">
@@ -20096,13 +20167,13 @@
         <v>21002</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>2063</v>
+        <v>2059</v>
       </c>
       <c r="C801" s="1" t="s">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="D801" s="1" t="s">
-        <v>2065</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="802" spans="1:5">
@@ -20110,13 +20181,13 @@
         <v>21003</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="C802" s="1" t="s">
-        <v>2067</v>
+        <v>2063</v>
       </c>
       <c r="D802" s="1" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="803" spans="1:5" ht="27.75">
@@ -20124,13 +20195,13 @@
         <v>21004</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>2071</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="804" spans="1:5" ht="27.75">
@@ -20138,13 +20209,13 @@
         <v>21005</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>2073</v>
+        <v>2069</v>
       </c>
       <c r="D804" s="2" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="805" spans="1:5" ht="27.75">
@@ -20152,13 +20223,13 @@
         <v>21006</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
       <c r="D805" s="2" t="s">
-        <v>2077</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="806" spans="1:5">
@@ -20166,13 +20237,13 @@
         <v>21007</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
       <c r="C806" s="1" t="s">
-        <v>2079</v>
+        <v>2075</v>
       </c>
       <c r="D806" s="1" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="807" spans="1:5" ht="27.75">
@@ -20180,13 +20251,13 @@
         <v>21008</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="808" spans="1:5">
@@ -20194,13 +20265,13 @@
         <v>21009</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="C808" s="1" t="s">
-        <v>2085</v>
+        <v>2081</v>
       </c>
       <c r="D808" s="1" t="s">
-        <v>2086</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="809" spans="1:5" ht="27.75">
@@ -20208,13 +20279,13 @@
         <v>21010</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
       <c r="C809" s="2" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
       <c r="D809" s="2" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="810" spans="1:5" ht="27.75">
@@ -20222,13 +20293,13 @@
         <v>21011</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="D810" s="2" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="811" spans="1:5" ht="27.75">
@@ -20236,13 +20307,13 @@
         <v>21012</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
       <c r="D811" s="2" t="s">
-        <v>2095</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="812" spans="1:5">
@@ -20250,16 +20321,16 @@
         <v>21013</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>2096</v>
+        <v>2092</v>
       </c>
       <c r="C812" s="1" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="D812" s="1" t="s">
-        <v>2099</v>
+        <v>2095</v>
       </c>
       <c r="E812" s="1" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="813" spans="1:5">
@@ -20267,13 +20338,13 @@
         <v>21014</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>2100</v>
+        <v>2096</v>
       </c>
       <c r="C813" s="1" t="s">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="D813" s="1" t="s">
-        <v>2102</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="814" spans="1:5">
@@ -20281,16 +20352,16 @@
         <v>21015</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>2103</v>
+        <v>2099</v>
       </c>
       <c r="C814" s="1" t="s">
-        <v>2105</v>
+        <v>2101</v>
       </c>
       <c r="D814" s="1" t="s">
-        <v>2106</v>
+        <v>2102</v>
       </c>
       <c r="E814" s="1" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="815" spans="1:5">
@@ -20298,13 +20369,13 @@
         <v>21016</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="C815" s="1" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
       <c r="D815" s="1" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="816" spans="1:5">
@@ -20312,68 +20383,68 @@
         <v>21017</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>2110</v>
+        <v>2106</v>
       </c>
       <c r="C816" s="1" t="s">
-        <v>2111</v>
+        <v>2107</v>
       </c>
       <c r="D816" s="1" t="s">
-        <v>2112</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="817" spans="2:5">
       <c r="B817" s="1" t="s">
-        <v>2113</v>
+        <v>2109</v>
       </c>
       <c r="C817" s="1" t="s">
         <v>434</v>
       </c>
       <c r="D817" s="1" t="s">
-        <v>2114</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="818" spans="2:5">
       <c r="B818" s="1" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="C818" s="1" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="D818" s="1" t="s">
-        <v>2117</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="819" spans="2:5">
       <c r="B819" s="1" t="s">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="C819" s="1" t="s">
-        <v>2119</v>
+        <v>2115</v>
       </c>
       <c r="D819" s="1" t="s">
-        <v>2120</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="820" spans="2:5">
       <c r="B820" s="1" t="s">
-        <v>2121</v>
+        <v>2117</v>
       </c>
       <c r="C820" s="1" t="s">
-        <v>2122</v>
+        <v>2118</v>
       </c>
       <c r="D820" s="1" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="821" spans="2:5">
       <c r="B821" s="1" t="s">
-        <v>2124</v>
+        <v>2120</v>
       </c>
       <c r="C821" s="1" t="s">
-        <v>2125</v>
+        <v>2121</v>
       </c>
       <c r="D821" s="1" t="s">
-        <v>2126</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="822" spans="2:5">
@@ -20381,159 +20452,159 @@
         <v>444</v>
       </c>
       <c r="C822" s="1" t="s">
-        <v>2127</v>
+        <v>2123</v>
       </c>
       <c r="D822" s="1" t="s">
-        <v>2128</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="823" spans="2:5">
       <c r="B823" s="1" t="s">
-        <v>2129</v>
+        <v>2125</v>
       </c>
       <c r="C823" s="1" t="s">
-        <v>2130</v>
+        <v>2126</v>
       </c>
       <c r="D823" s="1" t="s">
-        <v>2131</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="824" spans="2:5">
       <c r="B824" s="1" t="s">
-        <v>2132</v>
+        <v>2128</v>
       </c>
       <c r="C824" s="1" t="s">
-        <v>2133</v>
+        <v>2129</v>
       </c>
       <c r="D824" s="1" t="s">
-        <v>2134</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="825" spans="2:5">
       <c r="B825" s="1" t="s">
-        <v>2135</v>
+        <v>2131</v>
       </c>
       <c r="C825" s="1" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="D825" s="1" t="s">
-        <v>2138</v>
+        <v>2134</v>
       </c>
       <c r="E825" s="1" t="s">
-        <v>2136</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="826" spans="2:5">
       <c r="B826" s="1" t="s">
-        <v>2139</v>
+        <v>2135</v>
       </c>
       <c r="C826" s="1" t="s">
-        <v>2141</v>
+        <v>2137</v>
       </c>
       <c r="D826" s="1" t="s">
-        <v>2140</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="827" spans="2:5">
       <c r="B827" s="1" t="s">
-        <v>2142</v>
+        <v>2138</v>
       </c>
       <c r="C827" s="1" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="D827" s="1" t="s">
-        <v>2144</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="828" spans="2:5">
       <c r="B828" s="1" t="s">
-        <v>2145</v>
+        <v>2141</v>
       </c>
       <c r="C828" s="1" t="s">
-        <v>2146</v>
+        <v>2142</v>
       </c>
       <c r="D828" s="1" t="s">
-        <v>2147</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="829" spans="2:5">
       <c r="B829" s="1" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="C829" s="1" t="s">
-        <v>2149</v>
+        <v>2145</v>
       </c>
       <c r="D829" s="1" t="s">
-        <v>2150</v>
+        <v>2146</v>
       </c>
       <c r="E829" s="1" t="s">
-        <v>2151</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="830" spans="2:5">
       <c r="B830" s="1" t="s">
-        <v>2152</v>
+        <v>2148</v>
       </c>
       <c r="C830" s="1" t="s">
-        <v>2153</v>
+        <v>2149</v>
       </c>
       <c r="D830" s="1" t="s">
-        <v>2154</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="831" spans="2:5">
       <c r="B831" s="1" t="s">
-        <v>2155</v>
+        <v>2151</v>
       </c>
       <c r="C831" s="1" t="s">
-        <v>2156</v>
+        <v>2152</v>
       </c>
       <c r="D831" s="1" t="s">
-        <v>2157</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="832" spans="2:5">
       <c r="B832" s="1" t="s">
-        <v>2158</v>
+        <v>2154</v>
       </c>
       <c r="C832" s="1" t="s">
-        <v>2159</v>
+        <v>2155</v>
       </c>
       <c r="D832" s="1" t="s">
-        <v>2160</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="833" spans="2:4">
       <c r="B833" s="1" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
       <c r="C833" s="1" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="D833" s="1" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="834" spans="2:4">
       <c r="B834" s="1" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="C834" s="1" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="D834" s="1" t="s">
-        <v>2166</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="835" spans="2:4">
       <c r="B835" s="1" t="s">
-        <v>2167</v>
+        <v>2163</v>
       </c>
       <c r="C835" s="1" t="s">
-        <v>2168</v>
+        <v>2164</v>
       </c>
       <c r="D835" s="1" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
     </row>
   </sheetData>
@@ -20544,7 +20615,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BEDC60-BD86-4F0B-8906-B631C56865DE}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
@@ -20583,17 +20654,20 @@
     </row>
     <row r="3" spans="1:5">
       <c r="B3" t="s">
-        <v>1125</v>
+        <v>1577</v>
       </c>
       <c r="C3" t="s">
-        <v>1126</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C4" t="s">
         <v>1580</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>1581</v>
       </c>
     </row>
@@ -20604,27 +20678,67 @@
       <c r="C5" t="s">
         <v>1583</v>
       </c>
-      <c r="D5" t="s">
-        <v>1584</v>
-      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C6" t="s">
         <v>1585</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>1586</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>1587</v>
+        <v>2166</v>
       </c>
       <c r="C7" t="s">
-        <v>1588</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1589</v>
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2177</v>
       </c>
     </row>
   </sheetData>
@@ -20634,6 +20748,62 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D070E02D-D4DA-4042-9E24-5FF12F571A9A}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="2" max="2" width="12.19921875" customWidth="1"/>
+    <col min="3" max="3" width="14.19921875" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="B2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2185</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E327196-0A94-422A-A422-84A769DDFF6A}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
@@ -20691,34 +20861,34 @@
     </row>
     <row r="5" spans="1:5">
       <c r="B5" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C5" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C6" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C7" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="C8" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
     </row>
   </sheetData>

--- a/词表.xlsx
+++ b/词表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GRE\GRE-wordlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjliu\Desktop\GRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65437EB-42A0-4394-AA16-D15BE70F30F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF25ACE-8169-49B8-A44F-656E469104F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6010" yWindow="1300" windowWidth="19590" windowHeight="12290" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="2187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="2246">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5463,10 +5463,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>apthetic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>indifferent, uninterested</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6216,10 +6212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>untenbale</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>adj. 没有依据的, 站不住脚的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8046,10 +8038,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>浮漂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sustain, help, encourage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8814,6 +8802,251 @@
   </si>
   <si>
     <t>savor, enjoy, delighted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮漂, buoyancy 乐观</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inexplicable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 无法解释的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteoric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 迅速成功的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流星的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outright</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 彻底的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ephemeral, momentary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>permeating</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 渗透性的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spirited</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 生机勃勃的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vigorous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compassionate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有同情心的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>white-hot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白炽灯一样的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 抵消</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counterbalance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unqualifisd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 无保留的, 绝对的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qualify 限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conjure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 变出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mendacity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dhrieking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 尖叫, 嚎叫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>caterwauling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>croon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 低声吟唱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>precarious</t>
+  </si>
+  <si>
+    <t>adj. 不稳固的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tumultuous</t>
+  </si>
+  <si>
+    <t>adj. 动荡的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>galvanize</t>
+  </si>
+  <si>
+    <t>canned</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 老一套的, 公式化的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formulaic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expeditious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 迅速的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pecuniary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 金钱的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>candor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pulchritude</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equanimity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 镇定, 平和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 美丽, 标致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 坦诚, 直率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>palliative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. adj. 缓和</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apathetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>untenable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flinch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 退缩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dismissal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 解雇, 不理会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expiation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 赎罪, 补偿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frenzy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 狂热</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9153,13 +9386,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E835"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="15.1328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.3984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.4140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="35.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.25" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -9281,7 +9514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.75">
+    <row r="9" spans="1:5" ht="28">
       <c r="A9" s="1">
         <v>1008</v>
       </c>
@@ -9659,7 +9892,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27.75">
+    <row r="36" spans="1:5" ht="28">
       <c r="A36" s="1">
         <v>1035</v>
       </c>
@@ -9793,7 +10026,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="27.75">
+    <row r="46" spans="1:5" ht="28">
       <c r="A46" s="1">
         <v>2010</v>
       </c>
@@ -11791,7 +12024,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="27.75">
+    <row r="208" spans="1:5" ht="28">
       <c r="A208" s="1">
         <v>7014</v>
       </c>
@@ -12127,7 +12360,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="41.65">
+    <row r="235" spans="1:4" ht="42">
       <c r="A235" s="1">
         <v>7041</v>
       </c>
@@ -12399,7 +12632,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="27.75">
+    <row r="257" spans="1:4" ht="28">
       <c r="A257" s="1">
         <v>8013</v>
       </c>
@@ -12833,7 +13066,7 @@
         <v>667</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>670</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -12889,7 +13122,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="27.75">
+    <row r="295" spans="1:5" ht="28">
       <c r="A295" s="1">
         <v>9009</v>
       </c>
@@ -12928,7 +13161,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="41.65">
+    <row r="298" spans="1:5" ht="42">
       <c r="A298" s="1">
         <v>9012</v>
       </c>
@@ -12966,6 +13199,9 @@
       <c r="C300" s="1" t="s">
         <v>694</v>
       </c>
+      <c r="D300" s="1" t="s">
+        <v>696</v>
+      </c>
       <c r="E300" s="1" t="s">
         <v>695</v>
       </c>
@@ -13569,6 +13805,9 @@
       <c r="C345" s="1" t="s">
         <v>796</v>
       </c>
+      <c r="E345" s="1" t="s">
+        <v>2210</v>
+      </c>
     </row>
     <row r="346" spans="1:5">
       <c r="A346" s="1">
@@ -13816,7 +14055,7 @@
         <v>847</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>875</v>
@@ -13891,7 +14130,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="27.75">
+    <row r="370" spans="1:5" ht="28">
       <c r="A370" s="1">
         <v>10042</v>
       </c>
@@ -14379,7 +14618,7 @@
         <v>936</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -14736,7 +14975,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="27.75">
+    <row r="428" spans="1:5" ht="28">
       <c r="A428" s="1">
         <v>12009</v>
       </c>
@@ -14876,7 +15115,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="27.75">
+    <row r="438" spans="1:5" ht="28">
       <c r="A438" s="1">
         <v>12019</v>
       </c>
@@ -15303,7 +15542,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="27.75">
+    <row r="467" spans="1:5" ht="28">
       <c r="A467" s="1">
         <v>13009</v>
       </c>
@@ -15627,7 +15866,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="27.75">
+    <row r="488" spans="1:5" ht="28">
       <c r="A488" s="1">
         <v>13030</v>
       </c>
@@ -15829,7 +16068,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="27.75">
+    <row r="502" spans="1:5" ht="28">
       <c r="A502" s="1">
         <v>13044</v>
       </c>
@@ -16468,7 +16707,7 @@
         <v>1331</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="547" spans="1:5">
@@ -16580,13 +16819,13 @@
         <v>15005</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1354</v>
+        <v>2236</v>
       </c>
       <c r="C554" s="1" t="s">
         <v>1351</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="555" spans="1:5">
@@ -16594,13 +16833,13 @@
         <v>15006</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C555" s="1" t="s">
         <v>1351</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="556" spans="1:5">
@@ -16608,16 +16847,16 @@
         <v>15007</v>
       </c>
       <c r="B556" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C556" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="C556" s="1" t="s">
+      <c r="D556" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E556" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="D556" s="1" t="s">
-        <v>1361</v>
-      </c>
-      <c r="E556" s="1" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -16625,13 +16864,13 @@
         <v>15008</v>
       </c>
       <c r="B557" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C557" s="1" t="s">
         <v>1362</v>
       </c>
-      <c r="C557" s="1" t="s">
+      <c r="D557" s="1" t="s">
         <v>1363</v>
-      </c>
-      <c r="D557" s="1" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -16639,13 +16878,13 @@
         <v>15009</v>
       </c>
       <c r="B558" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C558" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="C558" s="1" t="s">
+      <c r="D558" s="1" t="s">
         <v>1366</v>
-      </c>
-      <c r="D558" s="1" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="559" spans="1:5">
@@ -16653,13 +16892,13 @@
         <v>15010</v>
       </c>
       <c r="B559" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D559" s="1" t="s">
         <v>1368</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -16667,16 +16906,16 @@
         <v>15011</v>
       </c>
       <c r="B560" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C560" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="C560" s="1" t="s">
-        <v>1371</v>
-      </c>
       <c r="D560" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -16684,13 +16923,13 @@
         <v>15012</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>1321</v>
@@ -16704,10 +16943,10 @@
         <v>223</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -16715,13 +16954,13 @@
         <v>15014</v>
       </c>
       <c r="B563" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D563" s="1" t="s">
         <v>1377</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D563" s="1" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -16729,13 +16968,13 @@
         <v>15015</v>
       </c>
       <c r="B564" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C564" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="C564" s="1" t="s">
+      <c r="D564" s="1" t="s">
         <v>1380</v>
-      </c>
-      <c r="D564" s="1" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="565" spans="1:5">
@@ -16743,13 +16982,13 @@
         <v>15016</v>
       </c>
       <c r="B565" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C565" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="C565" s="1" t="s">
-        <v>1383</v>
-      </c>
       <c r="D565" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="566" spans="1:5">
@@ -16757,13 +16996,13 @@
         <v>15017</v>
       </c>
       <c r="B566" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C566" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="C566" s="1" t="s">
+      <c r="D566" s="1" t="s">
         <v>1385</v>
-      </c>
-      <c r="D566" s="1" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="567" spans="1:5">
@@ -16771,13 +17010,13 @@
         <v>15018</v>
       </c>
       <c r="B567" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C567" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="C567" s="1" t="s">
+      <c r="D567" s="1" t="s">
         <v>1389</v>
-      </c>
-      <c r="D567" s="1" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -16788,10 +17027,10 @@
         <v>435</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -16799,13 +17038,13 @@
         <v>15020</v>
       </c>
       <c r="B569" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C569" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="C569" s="1" t="s">
+      <c r="D569" s="1" t="s">
         <v>1393</v>
-      </c>
-      <c r="D569" s="1" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="570" spans="1:5">
@@ -16813,13 +17052,13 @@
         <v>15021</v>
       </c>
       <c r="B570" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D570" s="1" t="s">
         <v>1395</v>
-      </c>
-      <c r="C570" s="1" t="s">
-        <v>1393</v>
-      </c>
-      <c r="D570" s="1" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="571" spans="1:5">
@@ -16827,16 +17066,16 @@
         <v>15022</v>
       </c>
       <c r="B571" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C571" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="C571" s="1" t="s">
+      <c r="D571" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="D571" s="1" t="s">
+      <c r="E571" s="1" t="s">
         <v>1399</v>
-      </c>
-      <c r="E571" s="1" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="572" spans="1:5">
@@ -16844,13 +17083,13 @@
         <v>15023</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="573" spans="1:5">
@@ -16858,13 +17097,13 @@
         <v>15024</v>
       </c>
       <c r="B573" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C573" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="C573" s="1" t="s">
+      <c r="D573" s="1" t="s">
         <v>1403</v>
-      </c>
-      <c r="D573" s="1" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -16872,13 +17111,13 @@
         <v>15025</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C574" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D574" s="1" t="s">
         <v>1403</v>
-      </c>
-      <c r="D574" s="1" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="575" spans="1:5">
@@ -16886,13 +17125,13 @@
         <v>15026</v>
       </c>
       <c r="B575" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D575" s="1" t="s">
         <v>1406</v>
-      </c>
-      <c r="C575" s="1" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D575" s="1" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="576" spans="1:5">
@@ -16900,13 +17139,13 @@
         <v>15027</v>
       </c>
       <c r="B576" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D576" s="1" t="s">
         <v>1407</v>
-      </c>
-      <c r="C576" s="1" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D576" s="1" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="577" spans="1:5">
@@ -16914,27 +17153,27 @@
         <v>15028</v>
       </c>
       <c r="B577" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D577" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="C577" s="1" t="s">
-        <v>1411</v>
-      </c>
-      <c r="D577" s="1" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="578" spans="1:5" ht="27.75">
+    </row>
+    <row r="578" spans="1:5" ht="28">
       <c r="A578" s="1">
         <v>15029</v>
       </c>
       <c r="B578" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C578" s="2" t="s">
         <v>1412</v>
       </c>
-      <c r="C578" s="2" t="s">
+      <c r="D578" s="1" t="s">
         <v>1413</v>
-      </c>
-      <c r="D578" s="1" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -16942,13 +17181,13 @@
         <v>15030</v>
       </c>
       <c r="B579" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C579" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="C579" s="1" t="s">
+      <c r="D579" s="1" t="s">
         <v>1416</v>
-      </c>
-      <c r="D579" s="1" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -16956,13 +17195,13 @@
         <v>15031</v>
       </c>
       <c r="B580" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C580" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D580" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C580" s="1" t="s">
-        <v>1416</v>
-      </c>
-      <c r="D580" s="1" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="581" spans="1:5">
@@ -16970,13 +17209,13 @@
         <v>15032</v>
       </c>
       <c r="B581" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D581" s="1" t="s">
         <v>1420</v>
-      </c>
-      <c r="C581" s="1" t="s">
-        <v>1416</v>
-      </c>
-      <c r="D581" s="1" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="582" spans="1:5">
@@ -16984,13 +17223,13 @@
         <v>15033</v>
       </c>
       <c r="B582" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C582" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="C582" s="1" t="s">
-        <v>1423</v>
-      </c>
       <c r="D582" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="583" spans="1:5">
@@ -16998,13 +17237,13 @@
         <v>15034</v>
       </c>
       <c r="B583" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C583" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="C583" s="1" t="s">
+      <c r="D583" s="1" t="s">
         <v>1425</v>
-      </c>
-      <c r="D583" s="1" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="584" spans="1:5">
@@ -17012,13 +17251,13 @@
         <v>15035</v>
       </c>
       <c r="B584" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C584" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="C584" s="1" t="s">
+      <c r="D584" s="1" t="s">
         <v>1428</v>
-      </c>
-      <c r="D584" s="1" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -17026,13 +17265,13 @@
         <v>15036</v>
       </c>
       <c r="B585" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D585" s="1" t="s">
         <v>1430</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="586" spans="1:5">
@@ -17040,13 +17279,13 @@
         <v>15037</v>
       </c>
       <c r="B586" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D586" s="1" t="s">
         <v>1432</v>
-      </c>
-      <c r="C586" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D586" s="1" t="s">
-        <v>1433</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -17054,16 +17293,16 @@
         <v>15038</v>
       </c>
       <c r="B587" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D587" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="C587" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D587" s="1" t="s">
+      <c r="E587" s="1" t="s">
         <v>1435</v>
-      </c>
-      <c r="E587" s="1" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -17071,13 +17310,13 @@
         <v>15039</v>
       </c>
       <c r="B588" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D588" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="C588" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D588" s="1" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -17085,13 +17324,13 @@
         <v>15040</v>
       </c>
       <c r="B589" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D589" s="1" t="s">
         <v>1439</v>
-      </c>
-      <c r="C589" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D589" s="1" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -17099,16 +17338,16 @@
         <v>15041</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -17116,13 +17355,13 @@
         <v>15042</v>
       </c>
       <c r="B591" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D591" s="1" t="s">
         <v>1443</v>
-      </c>
-      <c r="C591" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D591" s="1" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -17130,13 +17369,13 @@
         <v>15043</v>
       </c>
       <c r="B592" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C592" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="C592" s="1" t="s">
+      <c r="D592" s="1" t="s">
         <v>1446</v>
-      </c>
-      <c r="D592" s="1" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="593" spans="1:5">
@@ -17144,13 +17383,13 @@
         <v>15044</v>
       </c>
       <c r="B593" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C593" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="C593" s="1" t="s">
+      <c r="D593" s="1" t="s">
         <v>1449</v>
-      </c>
-      <c r="D593" s="1" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="594" spans="1:5">
@@ -17158,13 +17397,13 @@
         <v>15045</v>
       </c>
       <c r="B594" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C594" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="C594" s="1" t="s">
+      <c r="D594" s="1" t="s">
         <v>1452</v>
-      </c>
-      <c r="D594" s="1" t="s">
-        <v>1453</v>
       </c>
     </row>
     <row r="595" spans="1:5">
@@ -17172,16 +17411,16 @@
         <v>15046</v>
       </c>
       <c r="B595" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E595" s="1" t="s">
         <v>1454</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>1451</v>
-      </c>
-      <c r="E595" s="1" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="596" spans="1:5">
@@ -17189,13 +17428,13 @@
         <v>16001</v>
       </c>
       <c r="B596" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C596" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="C596" s="1" t="s">
+      <c r="D596" s="1" t="s">
         <v>1457</v>
-      </c>
-      <c r="D596" s="1" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="597" spans="1:5">
@@ -17203,13 +17442,13 @@
         <v>16002</v>
       </c>
       <c r="B597" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C597" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="C597" s="1" t="s">
+      <c r="D597" s="1" t="s">
         <v>1460</v>
-      </c>
-      <c r="D597" s="1" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="598" spans="1:5">
@@ -17217,13 +17456,13 @@
         <v>16003</v>
       </c>
       <c r="B598" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C598" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="C598" s="1" t="s">
+      <c r="D598" s="1" t="s">
         <v>1463</v>
-      </c>
-      <c r="D598" s="1" t="s">
-        <v>1464</v>
       </c>
     </row>
     <row r="599" spans="1:5">
@@ -17231,13 +17470,13 @@
         <v>16004</v>
       </c>
       <c r="B599" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C599" s="1" t="s">
         <v>1465</v>
       </c>
-      <c r="C599" s="1" t="s">
+      <c r="D599" s="1" t="s">
         <v>1466</v>
-      </c>
-      <c r="D599" s="1" t="s">
-        <v>1467</v>
       </c>
     </row>
     <row r="600" spans="1:5">
@@ -17245,13 +17484,13 @@
         <v>16005</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="601" spans="1:5">
@@ -17259,13 +17498,13 @@
         <v>16006</v>
       </c>
       <c r="B601" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C601" s="1" t="s">
         <v>1469</v>
       </c>
-      <c r="C601" s="1" t="s">
+      <c r="D601" s="1" t="s">
         <v>1470</v>
-      </c>
-      <c r="D601" s="1" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="602" spans="1:5">
@@ -17273,13 +17512,13 @@
         <v>16007</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C602" s="1" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="603" spans="1:5">
@@ -17287,13 +17526,13 @@
         <v>16008</v>
       </c>
       <c r="B603" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C603" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="C603" s="1" t="s">
+      <c r="D603" s="1" t="s">
         <v>1474</v>
-      </c>
-      <c r="D603" s="1" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="604" spans="1:5">
@@ -17301,13 +17540,13 @@
         <v>16009</v>
       </c>
       <c r="B604" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C604" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="C604" s="1" t="s">
+      <c r="D604" s="1" t="s">
         <v>1477</v>
-      </c>
-      <c r="D604" s="1" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="605" spans="1:5">
@@ -17315,13 +17554,13 @@
         <v>16010</v>
       </c>
       <c r="B605" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C605" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="C605" s="1" t="s">
+      <c r="D605" s="1" t="s">
         <v>1480</v>
-      </c>
-      <c r="D605" s="1" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="606" spans="1:5">
@@ -17329,13 +17568,13 @@
         <v>16011</v>
       </c>
       <c r="B606" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C606" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="C606" s="1" t="s">
+      <c r="D606" s="1" t="s">
         <v>1483</v>
-      </c>
-      <c r="D606" s="1" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="607" spans="1:5">
@@ -17343,13 +17582,13 @@
         <v>16012</v>
       </c>
       <c r="B607" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D607" s="1" t="s">
         <v>1485</v>
-      </c>
-      <c r="C607" s="1" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D607" s="1" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="608" spans="1:5">
@@ -17357,13 +17596,13 @@
         <v>16013</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="609" spans="1:5">
@@ -17371,13 +17610,13 @@
         <v>16014</v>
       </c>
       <c r="B609" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D609" s="1" t="s">
         <v>1488</v>
-      </c>
-      <c r="C609" s="1" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D609" s="1" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="610" spans="1:5">
@@ -17385,13 +17624,13 @@
         <v>16015</v>
       </c>
       <c r="B610" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D610" s="1" t="s">
         <v>1490</v>
-      </c>
-      <c r="C610" s="1" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D610" s="1" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="611" spans="1:5">
@@ -17399,13 +17638,13 @@
         <v>16016</v>
       </c>
       <c r="B611" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C611" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="C611" s="1" t="s">
-        <v>1493</v>
-      </c>
       <c r="D611" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="612" spans="1:5">
@@ -17413,13 +17652,13 @@
         <v>16017</v>
       </c>
       <c r="B612" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C612" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="C612" s="1" t="s">
+      <c r="D612" s="1" t="s">
         <v>1495</v>
-      </c>
-      <c r="D612" s="1" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="613" spans="1:5">
@@ -17427,13 +17666,13 @@
         <v>16018</v>
       </c>
       <c r="B613" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C613" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="C613" s="1" t="s">
-        <v>1498</v>
-      </c>
       <c r="D613" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="614" spans="1:5">
@@ -17441,13 +17680,13 @@
         <v>16019</v>
       </c>
       <c r="B614" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C614" s="1" t="s">
         <v>1499</v>
       </c>
-      <c r="C614" s="1" t="s">
-        <v>1500</v>
-      </c>
       <c r="D614" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="615" spans="1:5">
@@ -17455,13 +17694,13 @@
         <v>16020</v>
       </c>
       <c r="B615" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C615" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="C615" s="1" t="s">
+      <c r="D615" s="1" t="s">
         <v>1502</v>
-      </c>
-      <c r="D615" s="1" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="616" spans="1:5">
@@ -17469,13 +17708,13 @@
         <v>16021</v>
       </c>
       <c r="B616" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D616" s="1" t="s">
         <v>1504</v>
-      </c>
-      <c r="C616" s="1" t="s">
-        <v>1502</v>
-      </c>
-      <c r="D616" s="1" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="617" spans="1:5">
@@ -17483,16 +17722,16 @@
         <v>16022</v>
       </c>
       <c r="B617" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D617" s="1" t="s">
         <v>1506</v>
       </c>
-      <c r="C617" s="1" t="s">
-        <v>1502</v>
-      </c>
-      <c r="D617" s="1" t="s">
+      <c r="E617" s="1" t="s">
         <v>1507</v>
-      </c>
-      <c r="E617" s="1" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="618" spans="1:5">
@@ -17500,13 +17739,13 @@
         <v>16023</v>
       </c>
       <c r="B618" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C618" s="1" t="s">
         <v>1509</v>
       </c>
-      <c r="C618" s="1" t="s">
+      <c r="D618" s="1" t="s">
         <v>1510</v>
-      </c>
-      <c r="D618" s="1" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -17514,13 +17753,13 @@
         <v>16024</v>
       </c>
       <c r="B619" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C619" s="1" t="s">
         <v>1512</v>
       </c>
-      <c r="C619" s="1" t="s">
+      <c r="D619" s="1" t="s">
         <v>1513</v>
-      </c>
-      <c r="D619" s="1" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -17528,13 +17767,13 @@
         <v>16025</v>
       </c>
       <c r="B620" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D620" s="1" t="s">
         <v>1515</v>
-      </c>
-      <c r="C620" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D620" s="1" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -17542,13 +17781,13 @@
         <v>16026</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C621" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D621" s="1" t="s">
         <v>1517</v>
-      </c>
-      <c r="D621" s="1" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -17556,13 +17795,13 @@
         <v>16027</v>
       </c>
       <c r="B622" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C622" s="1" t="s">
         <v>1519</v>
       </c>
-      <c r="C622" s="1" t="s">
+      <c r="D622" s="1" t="s">
         <v>1520</v>
-      </c>
-      <c r="D622" s="1" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="623" spans="1:5">
@@ -17570,13 +17809,13 @@
         <v>16028</v>
       </c>
       <c r="B623" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D623" s="1" t="s">
         <v>1522</v>
-      </c>
-      <c r="C623" s="1" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D623" s="1" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -17584,16 +17823,16 @@
         <v>16029</v>
       </c>
       <c r="B624" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E624" s="1" t="s">
         <v>1524</v>
-      </c>
-      <c r="C624" s="1" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D624" s="1" t="s">
-        <v>1526</v>
-      </c>
-      <c r="E624" s="1" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -17601,13 +17840,13 @@
         <v>16030</v>
       </c>
       <c r="B625" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C625" s="1" t="s">
         <v>1527</v>
       </c>
-      <c r="C625" s="1" t="s">
+      <c r="D625" s="1" t="s">
         <v>1528</v>
-      </c>
-      <c r="D625" s="1" t="s">
-        <v>1529</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -17615,13 +17854,13 @@
         <v>16031</v>
       </c>
       <c r="B626" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C626" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="C626" s="1" t="s">
+      <c r="D626" s="1" t="s">
         <v>1531</v>
-      </c>
-      <c r="D626" s="1" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -17629,13 +17868,13 @@
         <v>16032</v>
       </c>
       <c r="B627" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C627" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="C627" s="1" t="s">
+      <c r="D627" s="1" t="s">
         <v>1534</v>
-      </c>
-      <c r="D627" s="1" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -17643,13 +17882,13 @@
         <v>16033</v>
       </c>
       <c r="B628" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C628" s="1" t="s">
         <v>1536</v>
       </c>
-      <c r="C628" s="1" t="s">
+      <c r="D628" s="1" t="s">
         <v>1537</v>
-      </c>
-      <c r="D628" s="1" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -17657,13 +17896,13 @@
         <v>16034</v>
       </c>
       <c r="B629" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C629" s="1" t="s">
         <v>1539</v>
       </c>
-      <c r="C629" s="1" t="s">
+      <c r="D629" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="D629" s="1" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="630" spans="1:5">
@@ -17671,13 +17910,13 @@
         <v>16035</v>
       </c>
       <c r="B630" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D630" s="1" t="s">
         <v>1542</v>
-      </c>
-      <c r="C630" s="1" t="s">
-        <v>1543</v>
-      </c>
-      <c r="D630" s="1" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -17685,13 +17924,13 @@
         <v>16036</v>
       </c>
       <c r="B631" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C631" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D631" s="1" t="s">
         <v>1545</v>
-      </c>
-      <c r="C631" s="1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="D631" s="1" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -17699,13 +17938,13 @@
         <v>16037</v>
       </c>
       <c r="B632" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D632" s="1" t="s">
         <v>1548</v>
-      </c>
-      <c r="C632" s="1" t="s">
-        <v>1549</v>
-      </c>
-      <c r="D632" s="1" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="633" spans="1:5">
@@ -17713,16 +17952,16 @@
         <v>16038</v>
       </c>
       <c r="B633" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E633" s="1" t="s">
         <v>1551</v>
-      </c>
-      <c r="C633" s="1" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D633" s="1" t="s">
-        <v>1554</v>
-      </c>
-      <c r="E633" s="1" t="s">
-        <v>1553</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -17730,13 +17969,13 @@
         <v>16039</v>
       </c>
       <c r="B634" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D634" s="1" t="s">
         <v>1555</v>
-      </c>
-      <c r="C634" s="1" t="s">
-        <v>1556</v>
-      </c>
-      <c r="D634" s="1" t="s">
-        <v>1557</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -17744,13 +17983,13 @@
         <v>16040</v>
       </c>
       <c r="B635" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D635" s="1" t="s">
         <v>1558</v>
-      </c>
-      <c r="C635" s="1" t="s">
-        <v>1559</v>
-      </c>
-      <c r="D635" s="1" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -17758,13 +17997,13 @@
         <v>16041</v>
       </c>
       <c r="B636" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C636" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D636" s="1" t="s">
         <v>1561</v>
-      </c>
-      <c r="C636" s="1" t="s">
-        <v>1562</v>
-      </c>
-      <c r="D636" s="1" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -17772,13 +18011,13 @@
         <v>17001</v>
       </c>
       <c r="B637" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D637" s="1" t="s">
         <v>1564</v>
-      </c>
-      <c r="C637" s="1" t="s">
-        <v>1565</v>
-      </c>
-      <c r="D637" s="1" t="s">
-        <v>1566</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -17786,16 +18025,16 @@
         <v>17002</v>
       </c>
       <c r="B638" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D638" s="1" t="s">
         <v>1566</v>
       </c>
-      <c r="C638" s="1" t="s">
+      <c r="E638" s="1" t="s">
         <v>1567</v>
-      </c>
-      <c r="D638" s="1" t="s">
-        <v>1568</v>
-      </c>
-      <c r="E638" s="1" t="s">
-        <v>1569</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -17803,16 +18042,16 @@
         <v>17003</v>
       </c>
       <c r="B639" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D639" s="1" t="s">
         <v>1570</v>
       </c>
-      <c r="C639" s="1" t="s">
+      <c r="E639" s="1" t="s">
         <v>1571</v>
-      </c>
-      <c r="D639" s="1" t="s">
-        <v>1572</v>
-      </c>
-      <c r="E639" s="1" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -17820,16 +18059,16 @@
         <v>17004</v>
       </c>
       <c r="B640" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C640" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D640" s="1" t="s">
         <v>1574</v>
       </c>
-      <c r="C640" s="1" t="s">
-        <v>1571</v>
-      </c>
-      <c r="D640" s="1" t="s">
-        <v>1576</v>
-      </c>
       <c r="E640" s="1" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="641" spans="1:5">
@@ -17837,13 +18076,13 @@
         <v>17005</v>
       </c>
       <c r="B641" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C641" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D641" s="1" t="s">
         <v>1587</v>
-      </c>
-      <c r="C641" s="1" t="s">
-        <v>1588</v>
-      </c>
-      <c r="D641" s="1" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -17851,13 +18090,13 @@
         <v>17006</v>
       </c>
       <c r="B642" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C642" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D642" s="1" t="s">
         <v>1590</v>
-      </c>
-      <c r="C642" s="1" t="s">
-        <v>1591</v>
-      </c>
-      <c r="D642" s="1" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="643" spans="1:5">
@@ -17865,13 +18104,13 @@
         <v>17007</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -17879,16 +18118,16 @@
         <v>17008</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="C644" s="1" t="s">
         <v>600</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="645" spans="1:5">
@@ -17896,16 +18135,16 @@
         <v>17009</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="C645" s="1" t="s">
         <v>600</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="646" spans="1:5">
@@ -17913,16 +18152,16 @@
         <v>17010</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="C646" s="1" t="s">
         <v>600</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="647" spans="1:5">
@@ -17930,16 +18169,16 @@
         <v>17011</v>
       </c>
       <c r="B647" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D647" s="1" t="s">
         <v>1604</v>
       </c>
-      <c r="C647" s="1" t="s">
+      <c r="E647" s="1" t="s">
         <v>1605</v>
-      </c>
-      <c r="D647" s="1" t="s">
-        <v>1606</v>
-      </c>
-      <c r="E647" s="1" t="s">
-        <v>1607</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -17947,13 +18186,13 @@
         <v>17012</v>
       </c>
       <c r="B648" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C648" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D648" s="1" t="s">
         <v>1608</v>
-      </c>
-      <c r="C648" s="1" t="s">
-        <v>1609</v>
-      </c>
-      <c r="D648" s="1" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="649" spans="1:5">
@@ -17961,16 +18200,16 @@
         <v>17013</v>
       </c>
       <c r="B649" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C649" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D649" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E649" s="1" t="s">
         <v>1611</v>
-      </c>
-      <c r="C649" s="1" t="s">
-        <v>1609</v>
-      </c>
-      <c r="D649" s="1" t="s">
-        <v>1612</v>
-      </c>
-      <c r="E649" s="1" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="650" spans="1:5">
@@ -17978,13 +18217,13 @@
         <v>17014</v>
       </c>
       <c r="B650" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C650" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D650" s="1" t="s">
         <v>1614</v>
-      </c>
-      <c r="C650" s="1" t="s">
-        <v>1615</v>
-      </c>
-      <c r="D650" s="1" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="651" spans="1:5">
@@ -17992,10 +18231,10 @@
         <v>17015</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="D651" s="1" t="s">
         <v>564</v>
@@ -18006,13 +18245,13 @@
         <v>17016</v>
       </c>
       <c r="B652" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C652" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D652" s="1" t="s">
         <v>1619</v>
-      </c>
-      <c r="C652" s="1" t="s">
-        <v>1620</v>
-      </c>
-      <c r="D652" s="1" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -18020,13 +18259,13 @@
         <v>17017</v>
       </c>
       <c r="B653" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D653" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C653" s="1" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D653" s="1" t="s">
-        <v>1624</v>
       </c>
     </row>
     <row r="654" spans="1:5">
@@ -18034,13 +18273,13 @@
         <v>17018</v>
       </c>
       <c r="B654" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C654" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D654" s="1" t="s">
         <v>1625</v>
-      </c>
-      <c r="C654" s="1" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D654" s="1" t="s">
-        <v>1627</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -18048,13 +18287,13 @@
         <v>17019</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="656" spans="1:5">
@@ -18062,16 +18301,16 @@
         <v>17020</v>
       </c>
       <c r="B656" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E656" s="1" t="s">
         <v>1629</v>
-      </c>
-      <c r="C656" s="1" t="s">
-        <v>1628</v>
-      </c>
-      <c r="D656" s="1" t="s">
-        <v>1630</v>
-      </c>
-      <c r="E656" s="1" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -18082,13 +18321,13 @@
         <v>384</v>
       </c>
       <c r="C657" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D657" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E657" s="1" t="s">
         <v>1632</v>
-      </c>
-      <c r="D657" s="1" t="s">
-        <v>1633</v>
-      </c>
-      <c r="E657" s="1" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -18096,13 +18335,13 @@
         <v>17022</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C658" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D658" s="1" t="s">
         <v>1633</v>
-      </c>
-      <c r="C658" s="1" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D658" s="1" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -18110,13 +18349,13 @@
         <v>17023</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C659" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D659" s="1" t="s">
         <v>1636</v>
-      </c>
-      <c r="C659" s="1" t="s">
-        <v>1637</v>
-      </c>
-      <c r="D659" s="1" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="660" spans="1:5">
@@ -18124,13 +18363,13 @@
         <v>17024</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C660" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D660" s="1" t="s">
         <v>1639</v>
-      </c>
-      <c r="C660" s="1" t="s">
-        <v>1640</v>
-      </c>
-      <c r="D660" s="1" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -18138,16 +18377,16 @@
         <v>17025</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C661" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D661" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E661" s="1" t="s">
         <v>1642</v>
-      </c>
-      <c r="C661" s="1" t="s">
-        <v>1643</v>
-      </c>
-      <c r="D661" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="E661" s="1" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="662" spans="1:5">
@@ -18155,13 +18394,13 @@
         <v>17026</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="663" spans="1:5">
@@ -18169,16 +18408,16 @@
         <v>17027</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C663" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D663" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E663" s="1" t="s">
         <v>1648</v>
-      </c>
-      <c r="C663" s="1" t="s">
-        <v>1649</v>
-      </c>
-      <c r="D663" s="1" t="s">
-        <v>1651</v>
-      </c>
-      <c r="E663" s="1" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -18186,13 +18425,13 @@
         <v>17028</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -18200,13 +18439,13 @@
         <v>17029</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C665" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D665" s="1" t="s">
         <v>1654</v>
-      </c>
-      <c r="C665" s="1" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D665" s="1" t="s">
-        <v>1656</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -18214,13 +18453,13 @@
         <v>17030</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D666" s="1" t="s">
         <v>1657</v>
-      </c>
-      <c r="C666" s="1" t="s">
-        <v>1658</v>
-      </c>
-      <c r="D666" s="1" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="667" spans="1:5">
@@ -18228,13 +18467,13 @@
         <v>17031</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C667" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D667" s="1" t="s">
         <v>1660</v>
-      </c>
-      <c r="C667" s="1" t="s">
-        <v>1661</v>
-      </c>
-      <c r="D667" s="1" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -18242,13 +18481,13 @@
         <v>17032</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D668" s="1" t="s">
         <v>1663</v>
-      </c>
-      <c r="C668" s="1" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D668" s="1" t="s">
-        <v>1665</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -18256,16 +18495,16 @@
         <v>17033</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D669" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="C669" s="1" t="s">
+      <c r="E669" s="1" t="s">
         <v>1667</v>
-      </c>
-      <c r="D669" s="1" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E669" s="1" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="670" spans="1:5">
@@ -18273,13 +18512,13 @@
         <v>17034</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D670" s="1" t="s">
         <v>1668</v>
-      </c>
-      <c r="C670" s="1" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D670" s="1" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -18287,13 +18526,13 @@
         <v>17035</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D671" s="1" t="s">
         <v>1671</v>
-      </c>
-      <c r="C671" s="1" t="s">
-        <v>1672</v>
-      </c>
-      <c r="D671" s="1" t="s">
-        <v>1673</v>
       </c>
     </row>
     <row r="672" spans="1:5">
@@ -18304,10 +18543,10 @@
         <v>747</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -18315,13 +18554,13 @@
         <v>17037</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C673" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D673" s="1" t="s">
         <v>1676</v>
-      </c>
-      <c r="D673" s="1" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="674" spans="1:5">
@@ -18329,16 +18568,16 @@
         <v>17038</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C674" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D674" s="1" t="s">
         <v>1679</v>
       </c>
-      <c r="C674" s="1" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D674" s="1" t="s">
-        <v>1681</v>
-      </c>
       <c r="E674" s="1" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="675" spans="1:5">
@@ -18346,16 +18585,16 @@
         <v>17039</v>
       </c>
       <c r="B675" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C675" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D675" s="1" t="s">
         <v>1682</v>
       </c>
-      <c r="C675" s="1" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D675" s="1" t="s">
-        <v>1684</v>
-      </c>
       <c r="E675" s="1" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="676" spans="1:5">
@@ -18363,13 +18602,13 @@
         <v>17040</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C676" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D676" s="1" t="s">
         <v>1685</v>
-      </c>
-      <c r="C676" s="1" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D676" s="1" t="s">
-        <v>1687</v>
       </c>
     </row>
     <row r="677" spans="1:5">
@@ -18377,13 +18616,13 @@
         <v>17041</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C677" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D677" s="1" t="s">
         <v>1688</v>
-      </c>
-      <c r="C677" s="1" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D677" s="1" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="678" spans="1:5">
@@ -18391,27 +18630,27 @@
         <v>17042</v>
       </c>
       <c r="B678" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D678" s="1" t="s">
         <v>1691</v>
       </c>
-      <c r="C678" s="1" t="s">
-        <v>1692</v>
-      </c>
-      <c r="D678" s="1" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="679" spans="1:5" ht="27.75">
+    </row>
+    <row r="679" spans="1:5" ht="28">
       <c r="A679" s="1">
         <v>17043</v>
       </c>
       <c r="B679" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C679" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D679" s="1" t="s">
         <v>1694</v>
-      </c>
-      <c r="C679" s="2" t="s">
-        <v>1695</v>
-      </c>
-      <c r="D679" s="1" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="680" spans="1:5">
@@ -18419,13 +18658,13 @@
         <v>17044</v>
       </c>
       <c r="B680" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D680" s="1" t="s">
         <v>1697</v>
-      </c>
-      <c r="C680" s="1" t="s">
-        <v>1698</v>
-      </c>
-      <c r="D680" s="1" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="681" spans="1:5">
@@ -18433,13 +18672,13 @@
         <v>17045</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="682" spans="1:5">
@@ -18447,13 +18686,13 @@
         <v>17046</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>481</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="683" spans="1:5">
@@ -18461,16 +18700,16 @@
         <v>18001</v>
       </c>
       <c r="B683" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D683" s="1" t="s">
         <v>1704</v>
       </c>
-      <c r="C683" s="1" t="s">
+      <c r="E683" s="1" t="s">
         <v>1705</v>
-      </c>
-      <c r="D683" s="1" t="s">
-        <v>1706</v>
-      </c>
-      <c r="E683" s="1" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="684" spans="1:5">
@@ -18478,13 +18717,13 @@
         <v>18002</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="685" spans="1:5">
@@ -18492,13 +18731,13 @@
         <v>18003</v>
       </c>
       <c r="B685" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C685" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D685" s="1" t="s">
         <v>1710</v>
-      </c>
-      <c r="C685" s="1" t="s">
-        <v>1711</v>
-      </c>
-      <c r="D685" s="1" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="686" spans="1:5">
@@ -18506,13 +18745,13 @@
         <v>18004</v>
       </c>
       <c r="B686" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C686" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D686" s="1" t="s">
         <v>1713</v>
-      </c>
-      <c r="C686" s="1" t="s">
-        <v>1714</v>
-      </c>
-      <c r="D686" s="1" t="s">
-        <v>1715</v>
       </c>
     </row>
     <row r="687" spans="1:5">
@@ -18520,13 +18759,13 @@
         <v>18005</v>
       </c>
       <c r="B687" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C687" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D687" s="1" t="s">
         <v>1716</v>
-      </c>
-      <c r="C687" s="1" t="s">
-        <v>1717</v>
-      </c>
-      <c r="D687" s="1" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="688" spans="1:5">
@@ -18534,16 +18773,16 @@
         <v>18006</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="C688" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D688" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E688" s="1" t="s">
         <v>1717</v>
-      </c>
-      <c r="D688" s="1" t="s">
-        <v>1716</v>
-      </c>
-      <c r="E688" s="1" t="s">
-        <v>1719</v>
       </c>
     </row>
     <row r="689" spans="1:5">
@@ -18551,13 +18790,13 @@
         <v>18007</v>
       </c>
       <c r="B689" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C689" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D689" s="1" t="s">
         <v>1720</v>
-      </c>
-      <c r="C689" s="1" t="s">
-        <v>1721</v>
-      </c>
-      <c r="D689" s="1" t="s">
-        <v>1722</v>
       </c>
     </row>
     <row r="690" spans="1:5">
@@ -18565,13 +18804,13 @@
         <v>18008</v>
       </c>
       <c r="B690" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D690" s="1" t="s">
         <v>1723</v>
-      </c>
-      <c r="C690" s="1" t="s">
-        <v>1724</v>
-      </c>
-      <c r="D690" s="1" t="s">
-        <v>1725</v>
       </c>
     </row>
     <row r="691" spans="1:5">
@@ -18579,16 +18818,16 @@
         <v>18009</v>
       </c>
       <c r="B691" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D691" s="1" t="s">
         <v>1726</v>
       </c>
-      <c r="C691" s="1" t="s">
+      <c r="E691" s="1" t="s">
         <v>1727</v>
-      </c>
-      <c r="D691" s="1" t="s">
-        <v>1728</v>
-      </c>
-      <c r="E691" s="1" t="s">
-        <v>1729</v>
       </c>
     </row>
     <row r="692" spans="1:5">
@@ -18596,16 +18835,16 @@
         <v>18010</v>
       </c>
       <c r="B692" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D692" s="1" t="s">
         <v>1730</v>
       </c>
-      <c r="C692" s="1" t="s">
+      <c r="E692" s="1" t="s">
         <v>1731</v>
-      </c>
-      <c r="D692" s="1" t="s">
-        <v>1732</v>
-      </c>
-      <c r="E692" s="1" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="693" spans="1:5">
@@ -18613,13 +18852,13 @@
         <v>18011</v>
       </c>
       <c r="B693" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D693" s="1" t="s">
         <v>1734</v>
-      </c>
-      <c r="C693" s="1" t="s">
-        <v>1735</v>
-      </c>
-      <c r="D693" s="1" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="694" spans="1:5">
@@ -18627,13 +18866,13 @@
         <v>18012</v>
       </c>
       <c r="B694" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D694" s="1" t="s">
         <v>1737</v>
-      </c>
-      <c r="C694" s="1" t="s">
-        <v>1738</v>
-      </c>
-      <c r="D694" s="1" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="695" spans="1:5">
@@ -18641,13 +18880,13 @@
         <v>18013</v>
       </c>
       <c r="B695" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D695" s="1" t="s">
         <v>1740</v>
-      </c>
-      <c r="C695" s="1" t="s">
-        <v>1741</v>
-      </c>
-      <c r="D695" s="1" t="s">
-        <v>1742</v>
       </c>
     </row>
     <row r="696" spans="1:5">
@@ -18658,10 +18897,10 @@
         <v>114</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="D696" s="1" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="697" spans="1:5">
@@ -18669,13 +18908,13 @@
         <v>18015</v>
       </c>
       <c r="B697" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D697" s="1" t="s">
         <v>1745</v>
-      </c>
-      <c r="C697" s="1" t="s">
-        <v>1746</v>
-      </c>
-      <c r="D697" s="1" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="698" spans="1:5">
@@ -18683,13 +18922,13 @@
         <v>18016</v>
       </c>
       <c r="B698" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D698" s="1" t="s">
         <v>1748</v>
-      </c>
-      <c r="C698" s="1" t="s">
-        <v>1749</v>
-      </c>
-      <c r="D698" s="1" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="699" spans="1:5">
@@ -18697,16 +18936,16 @@
         <v>18017</v>
       </c>
       <c r="B699" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D699" s="1" t="s">
         <v>1751</v>
       </c>
-      <c r="C699" s="1" t="s">
+      <c r="E699" s="1" t="s">
         <v>1752</v>
-      </c>
-      <c r="D699" s="1" t="s">
-        <v>1753</v>
-      </c>
-      <c r="E699" s="1" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="700" spans="1:5">
@@ -18714,13 +18953,13 @@
         <v>18018</v>
       </c>
       <c r="B700" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C700" s="1" t="s">
         <v>1753</v>
       </c>
-      <c r="C700" s="1" t="s">
-        <v>1755</v>
-      </c>
       <c r="D700" s="1" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="701" spans="1:5">
@@ -18728,13 +18967,13 @@
         <v>18019</v>
       </c>
       <c r="B701" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D701" s="1" t="s">
         <v>1757</v>
-      </c>
-      <c r="C701" s="1" t="s">
-        <v>1758</v>
-      </c>
-      <c r="D701" s="1" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="702" spans="1:5">
@@ -18742,13 +18981,13 @@
         <v>18020</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="C702" s="1" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="D702" s="1" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="703" spans="1:5">
@@ -18756,13 +18995,13 @@
         <v>18021</v>
       </c>
       <c r="B703" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C703" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D703" s="1" t="s">
         <v>1762</v>
-      </c>
-      <c r="C703" s="1" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D703" s="1" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="704" spans="1:5">
@@ -18770,13 +19009,13 @@
         <v>18022</v>
       </c>
       <c r="B704" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D704" s="1" t="s">
         <v>1765</v>
-      </c>
-      <c r="C704" s="1" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D704" s="1" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -18784,13 +19023,13 @@
         <v>18023</v>
       </c>
       <c r="B705" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C705" s="1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D705" s="1" t="s">
         <v>1768</v>
-      </c>
-      <c r="C705" s="1" t="s">
-        <v>1769</v>
-      </c>
-      <c r="D705" s="1" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -18798,13 +19037,13 @@
         <v>18024</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="C706" s="1" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="D706" s="1" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -18812,13 +19051,13 @@
         <v>18025</v>
       </c>
       <c r="B707" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C707" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D707" s="1" t="s">
         <v>1773</v>
-      </c>
-      <c r="C707" s="1" t="s">
-        <v>1774</v>
-      </c>
-      <c r="D707" s="1" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -18826,13 +19065,13 @@
         <v>18026</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="C708" s="1" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="D708" s="1" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -18840,13 +19079,13 @@
         <v>18027</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="C709" s="1" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="D709" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -18854,13 +19093,13 @@
         <v>18028</v>
       </c>
       <c r="B710" s="1" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="C710" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D710" s="1" t="s">
         <v>1779</v>
-      </c>
-      <c r="D710" s="1" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -18868,13 +19107,13 @@
         <v>18029</v>
       </c>
       <c r="B711" s="1" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C711" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D711" s="1" t="s">
         <v>1782</v>
-      </c>
-      <c r="C711" s="1" t="s">
-        <v>1783</v>
-      </c>
-      <c r="D711" s="1" t="s">
-        <v>1784</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -18882,24 +19121,24 @@
         <v>18030</v>
       </c>
       <c r="B712" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C712" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D712" s="1" t="s">
         <v>1785</v>
       </c>
-      <c r="C712" s="1" t="s">
-        <v>1786</v>
-      </c>
-      <c r="D712" s="1" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="713" spans="1:4" ht="27.75">
+    </row>
+    <row r="713" spans="1:4" ht="28">
       <c r="A713" s="1">
         <v>18031</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -18907,13 +19146,13 @@
         <v>18032</v>
       </c>
       <c r="B714" s="1" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D714" s="1" t="s">
         <v>1790</v>
-      </c>
-      <c r="C714" s="1" t="s">
-        <v>1791</v>
-      </c>
-      <c r="D714" s="1" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -18921,13 +19160,13 @@
         <v>18033</v>
       </c>
       <c r="B715" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D715" s="1" t="s">
         <v>1793</v>
-      </c>
-      <c r="C715" s="1" t="s">
-        <v>1794</v>
-      </c>
-      <c r="D715" s="1" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -18935,13 +19174,13 @@
         <v>18034</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="C716" s="1" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="D716" s="1" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -18949,13 +19188,13 @@
         <v>18035</v>
       </c>
       <c r="B717" s="1" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D717" s="1" t="s">
         <v>1798</v>
-      </c>
-      <c r="C717" s="1" t="s">
-        <v>1799</v>
-      </c>
-      <c r="D717" s="1" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -18963,13 +19202,13 @@
         <v>18036</v>
       </c>
       <c r="B718" s="1" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="C718" s="1" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="D718" s="1" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -18977,13 +19216,13 @@
         <v>18037</v>
       </c>
       <c r="B719" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C719" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D719" s="1" t="s">
         <v>1803</v>
-      </c>
-      <c r="C719" s="1" t="s">
-        <v>1804</v>
-      </c>
-      <c r="D719" s="1" t="s">
-        <v>1805</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -18991,13 +19230,13 @@
         <v>18038</v>
       </c>
       <c r="B720" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C720" s="1" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D720" s="1" t="s">
         <v>1806</v>
-      </c>
-      <c r="C720" s="1" t="s">
-        <v>1807</v>
-      </c>
-      <c r="D720" s="1" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="721" spans="1:5">
@@ -19005,16 +19244,16 @@
         <v>18039</v>
       </c>
       <c r="B721" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C721" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D721" s="1" t="s">
         <v>1809</v>
       </c>
-      <c r="C721" s="1" t="s">
+      <c r="E721" s="1" t="s">
         <v>1810</v>
-      </c>
-      <c r="D721" s="1" t="s">
-        <v>1811</v>
-      </c>
-      <c r="E721" s="1" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="722" spans="1:5">
@@ -19022,13 +19261,13 @@
         <v>18040</v>
       </c>
       <c r="B722" s="1" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="C722" s="1" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="D722" s="1" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="723" spans="1:5">
@@ -19036,13 +19275,13 @@
         <v>18041</v>
       </c>
       <c r="B723" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C723" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D723" s="1" t="s">
         <v>1815</v>
-      </c>
-      <c r="C723" s="1" t="s">
-        <v>1816</v>
-      </c>
-      <c r="D723" s="1" t="s">
-        <v>1817</v>
       </c>
     </row>
     <row r="724" spans="1:5">
@@ -19050,13 +19289,13 @@
         <v>19001</v>
       </c>
       <c r="B724" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C724" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D724" s="1" t="s">
         <v>1820</v>
-      </c>
-      <c r="C724" s="1" t="s">
-        <v>1821</v>
-      </c>
-      <c r="D724" s="1" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="725" spans="1:5">
@@ -19064,13 +19303,13 @@
         <v>19002</v>
       </c>
       <c r="B725" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C725" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D725" s="1" t="s">
         <v>1824</v>
-      </c>
-      <c r="C725" s="1" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D725" s="1" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="726" spans="1:5">
@@ -19078,13 +19317,13 @@
         <v>19003</v>
       </c>
       <c r="B726" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C726" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D726" s="1" t="s">
         <v>1827</v>
-      </c>
-      <c r="C726" s="1" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D726" s="1" t="s">
-        <v>1829</v>
       </c>
     </row>
     <row r="727" spans="1:5">
@@ -19092,13 +19331,13 @@
         <v>19004</v>
       </c>
       <c r="B727" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C727" s="1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D727" s="1" t="s">
         <v>1830</v>
-      </c>
-      <c r="C727" s="1" t="s">
-        <v>1831</v>
-      </c>
-      <c r="D727" s="1" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="728" spans="1:5">
@@ -19106,13 +19345,13 @@
         <v>19005</v>
       </c>
       <c r="B728" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C728" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D728" s="1" t="s">
         <v>1833</v>
-      </c>
-      <c r="C728" s="1" t="s">
-        <v>1834</v>
-      </c>
-      <c r="D728" s="1" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="729" spans="1:5">
@@ -19120,13 +19359,13 @@
         <v>19006</v>
       </c>
       <c r="B729" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C729" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D729" s="1" t="s">
         <v>1836</v>
-      </c>
-      <c r="C729" s="1" t="s">
-        <v>1837</v>
-      </c>
-      <c r="D729" s="1" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -19134,13 +19373,13 @@
         <v>19007</v>
       </c>
       <c r="B730" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C730" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D730" s="1" t="s">
         <v>1839</v>
-      </c>
-      <c r="C730" s="1" t="s">
-        <v>1840</v>
-      </c>
-      <c r="D730" s="1" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="731" spans="1:5">
@@ -19148,16 +19387,16 @@
         <v>19008</v>
       </c>
       <c r="B731" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C731" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D731" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E731" s="1" t="s">
         <v>1842</v>
-      </c>
-      <c r="C731" s="1" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D731" s="1" t="s">
-        <v>1845</v>
-      </c>
-      <c r="E731" s="1" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="732" spans="1:5">
@@ -19165,13 +19404,13 @@
         <v>19009</v>
       </c>
       <c r="B732" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C732" s="1" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E732" s="1" t="s">
         <v>1846</v>
-      </c>
-      <c r="C732" s="1" t="s">
-        <v>1847</v>
-      </c>
-      <c r="E732" s="1" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="733" spans="1:5">
@@ -19179,13 +19418,13 @@
         <v>19010</v>
       </c>
       <c r="B733" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C733" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D733" s="1" t="s">
         <v>1849</v>
-      </c>
-      <c r="C733" s="1" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D733" s="1" t="s">
-        <v>1851</v>
       </c>
     </row>
     <row r="734" spans="1:5">
@@ -19193,13 +19432,13 @@
         <v>19011</v>
       </c>
       <c r="B734" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C734" s="1" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D734" s="1" t="s">
         <v>1852</v>
-      </c>
-      <c r="C734" s="1" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D734" s="1" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="735" spans="1:5">
@@ -19207,16 +19446,16 @@
         <v>19012</v>
       </c>
       <c r="B735" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C735" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D735" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E735" s="1" t="s">
         <v>1855</v>
-      </c>
-      <c r="C735" s="1" t="s">
-        <v>1856</v>
-      </c>
-      <c r="D735" s="1" t="s">
-        <v>1858</v>
-      </c>
-      <c r="E735" s="1" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="736" spans="1:5">
@@ -19224,13 +19463,13 @@
         <v>19013</v>
       </c>
       <c r="B736" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C736" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D736" s="1" t="s">
         <v>1859</v>
-      </c>
-      <c r="C736" s="1" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D736" s="1" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="737" spans="1:5">
@@ -19238,13 +19477,13 @@
         <v>19014</v>
       </c>
       <c r="B737" s="1" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C737" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D737" s="1" t="s">
         <v>1862</v>
-      </c>
-      <c r="C737" s="1" t="s">
-        <v>1863</v>
-      </c>
-      <c r="D737" s="1" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="738" spans="1:5">
@@ -19252,13 +19491,13 @@
         <v>19015</v>
       </c>
       <c r="B738" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C738" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D738" s="1" t="s">
         <v>1865</v>
-      </c>
-      <c r="C738" s="1" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D738" s="1" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="739" spans="1:5">
@@ -19266,27 +19505,27 @@
         <v>19016</v>
       </c>
       <c r="B739" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C739" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D739" s="1" t="s">
         <v>1868</v>
       </c>
-      <c r="C739" s="1" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D739" s="1" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="740" spans="1:5" ht="27.75">
+    </row>
+    <row r="740" spans="1:5" ht="28">
       <c r="A740" s="1">
         <v>19017</v>
       </c>
       <c r="B740" s="1" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C740" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D740" s="2" t="s">
         <v>1871</v>
-      </c>
-      <c r="C740" s="2" t="s">
-        <v>1872</v>
-      </c>
-      <c r="D740" s="2" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="741" spans="1:5">
@@ -19294,13 +19533,13 @@
         <v>19018</v>
       </c>
       <c r="B741" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C741" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D741" s="1" t="s">
         <v>1874</v>
-      </c>
-      <c r="C741" s="1" t="s">
-        <v>1875</v>
-      </c>
-      <c r="D741" s="1" t="s">
-        <v>1876</v>
       </c>
     </row>
     <row r="742" spans="1:5">
@@ -19308,13 +19547,13 @@
         <v>19019</v>
       </c>
       <c r="B742" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C742" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D742" s="1" t="s">
         <v>1877</v>
-      </c>
-      <c r="C742" s="1" t="s">
-        <v>1878</v>
-      </c>
-      <c r="D742" s="1" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="743" spans="1:5">
@@ -19322,13 +19561,13 @@
         <v>19020</v>
       </c>
       <c r="B743" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C743" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D743" s="1" t="s">
         <v>1880</v>
-      </c>
-      <c r="C743" s="1" t="s">
-        <v>1881</v>
-      </c>
-      <c r="D743" s="1" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="744" spans="1:5">
@@ -19336,27 +19575,27 @@
         <v>19021</v>
       </c>
       <c r="B744" s="1" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C744" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D744" s="1" t="s">
         <v>1883</v>
       </c>
-      <c r="C744" s="1" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D744" s="1" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="745" spans="1:5" ht="27.75">
+    </row>
+    <row r="745" spans="1:5" ht="28">
       <c r="A745" s="1">
         <v>19022</v>
       </c>
       <c r="B745" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C745" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D745" s="2" t="s">
         <v>1886</v>
-      </c>
-      <c r="C745" s="2" t="s">
-        <v>1887</v>
-      </c>
-      <c r="D745" s="2" t="s">
-        <v>1888</v>
       </c>
     </row>
     <row r="746" spans="1:5">
@@ -19364,13 +19603,13 @@
         <v>19023</v>
       </c>
       <c r="B746" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C746" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D746" s="1" t="s">
         <v>1889</v>
-      </c>
-      <c r="C746" s="1" t="s">
-        <v>1890</v>
-      </c>
-      <c r="D746" s="1" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="747" spans="1:5">
@@ -19378,13 +19617,13 @@
         <v>19024</v>
       </c>
       <c r="B747" s="1" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C747" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D747" s="1" t="s">
         <v>1892</v>
-      </c>
-      <c r="C747" s="1" t="s">
-        <v>1893</v>
-      </c>
-      <c r="D747" s="1" t="s">
-        <v>1894</v>
       </c>
     </row>
     <row r="748" spans="1:5">
@@ -19395,10 +19634,10 @@
         <v>59</v>
       </c>
       <c r="C748" s="1" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="D748" s="1" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="749" spans="1:5">
@@ -19406,13 +19645,13 @@
         <v>19026</v>
       </c>
       <c r="B749" s="1" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="C749" s="1" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="D749" s="1" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="750" spans="1:5">
@@ -19420,16 +19659,16 @@
         <v>19027</v>
       </c>
       <c r="B750" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C750" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D750" s="1" t="s">
         <v>1899</v>
       </c>
-      <c r="C750" s="1" t="s">
+      <c r="E750" s="1" t="s">
         <v>1900</v>
-      </c>
-      <c r="D750" s="1" t="s">
-        <v>1901</v>
-      </c>
-      <c r="E750" s="1" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="751" spans="1:5">
@@ -19437,16 +19676,16 @@
         <v>19028</v>
       </c>
       <c r="B751" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C751" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D751" s="1" t="s">
         <v>1903</v>
       </c>
-      <c r="C751" s="1" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D751" s="1" t="s">
-        <v>1905</v>
-      </c>
       <c r="E751" s="1" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="752" spans="1:5">
@@ -19454,13 +19693,13 @@
         <v>19029</v>
       </c>
       <c r="B752" s="1" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C752" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D752" s="1" t="s">
         <v>1906</v>
-      </c>
-      <c r="C752" s="1" t="s">
-        <v>1907</v>
-      </c>
-      <c r="D752" s="1" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="753" spans="1:5">
@@ -19468,13 +19707,13 @@
         <v>19030</v>
       </c>
       <c r="B753" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C753" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D753" s="1" t="s">
         <v>1909</v>
-      </c>
-      <c r="C753" s="1" t="s">
-        <v>1910</v>
-      </c>
-      <c r="D753" s="1" t="s">
-        <v>1911</v>
       </c>
     </row>
     <row r="754" spans="1:5">
@@ -19482,13 +19721,13 @@
         <v>19031</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="C754" s="1" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="D754" s="1" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="755" spans="1:5">
@@ -19496,13 +19735,13 @@
         <v>19032</v>
       </c>
       <c r="B755" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C755" s="1" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D755" s="1" t="s">
         <v>1914</v>
-      </c>
-      <c r="C755" s="1" t="s">
-        <v>1915</v>
-      </c>
-      <c r="D755" s="1" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="756" spans="1:5">
@@ -19510,13 +19749,13 @@
         <v>19033</v>
       </c>
       <c r="B756" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C756" s="1" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D756" s="1" t="s">
         <v>1917</v>
-      </c>
-      <c r="C756" s="1" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D756" s="1" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="757" spans="1:5">
@@ -19524,16 +19763,16 @@
         <v>20001</v>
       </c>
       <c r="B757" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C757" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D757" s="1" t="s">
         <v>1920</v>
       </c>
-      <c r="C757" s="1" t="s">
+      <c r="E757" s="1" t="s">
         <v>1921</v>
-      </c>
-      <c r="D757" s="1" t="s">
-        <v>1922</v>
-      </c>
-      <c r="E757" s="1" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="758" spans="1:5">
@@ -19541,13 +19780,13 @@
         <v>20002</v>
       </c>
       <c r="B758" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C758" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D758" s="1" t="s">
         <v>1924</v>
-      </c>
-      <c r="C758" s="1" t="s">
-        <v>1925</v>
-      </c>
-      <c r="D758" s="1" t="s">
-        <v>1926</v>
       </c>
     </row>
     <row r="759" spans="1:5">
@@ -19555,13 +19794,13 @@
         <v>20003</v>
       </c>
       <c r="B759" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C759" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D759" s="1" t="s">
         <v>1927</v>
-      </c>
-      <c r="C759" s="1" t="s">
-        <v>1928</v>
-      </c>
-      <c r="D759" s="1" t="s">
-        <v>1929</v>
       </c>
     </row>
     <row r="760" spans="1:5">
@@ -19569,13 +19808,13 @@
         <v>20004</v>
       </c>
       <c r="B760" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C760" s="1" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D760" s="1" t="s">
         <v>1930</v>
-      </c>
-      <c r="C760" s="1" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D760" s="1" t="s">
-        <v>1932</v>
       </c>
     </row>
     <row r="761" spans="1:5">
@@ -19583,13 +19822,13 @@
         <v>20005</v>
       </c>
       <c r="B761" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C761" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D761" s="1" t="s">
         <v>1933</v>
-      </c>
-      <c r="C761" s="1" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D761" s="1" t="s">
-        <v>1935</v>
       </c>
     </row>
     <row r="762" spans="1:5">
@@ -19597,13 +19836,13 @@
         <v>20006</v>
       </c>
       <c r="B762" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C762" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D762" s="1" t="s">
         <v>1936</v>
-      </c>
-      <c r="C762" s="1" t="s">
-        <v>1937</v>
-      </c>
-      <c r="D762" s="1" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="763" spans="1:5">
@@ -19611,13 +19850,13 @@
         <v>20007</v>
       </c>
       <c r="B763" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C763" s="1" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D763" s="1" t="s">
         <v>1939</v>
-      </c>
-      <c r="C763" s="1" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D763" s="1" t="s">
-        <v>1941</v>
       </c>
     </row>
     <row r="764" spans="1:5">
@@ -19625,13 +19864,13 @@
         <v>20008</v>
       </c>
       <c r="B764" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C764" s="1" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D764" s="1" t="s">
         <v>1942</v>
-      </c>
-      <c r="C764" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D764" s="1" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="765" spans="1:5">
@@ -19639,13 +19878,13 @@
         <v>20009</v>
       </c>
       <c r="B765" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C765" s="1" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D765" s="1" t="s">
         <v>1945</v>
-      </c>
-      <c r="C765" s="1" t="s">
-        <v>1946</v>
-      </c>
-      <c r="D765" s="1" t="s">
-        <v>1947</v>
       </c>
     </row>
     <row r="766" spans="1:5">
@@ -19653,16 +19892,16 @@
         <v>20010</v>
       </c>
       <c r="B766" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C766" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D766" s="1" t="s">
         <v>1948</v>
       </c>
-      <c r="C766" s="1" t="s">
+      <c r="E766" s="1" t="s">
         <v>1949</v>
-      </c>
-      <c r="D766" s="1" t="s">
-        <v>1950</v>
-      </c>
-      <c r="E766" s="1" t="s">
-        <v>1951</v>
       </c>
     </row>
     <row r="767" spans="1:5">
@@ -19670,13 +19909,13 @@
         <v>20011</v>
       </c>
       <c r="B767" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C767" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D767" s="1" t="s">
         <v>1952</v>
-      </c>
-      <c r="C767" s="1" t="s">
-        <v>1953</v>
-      </c>
-      <c r="D767" s="1" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="768" spans="1:5">
@@ -19684,13 +19923,13 @@
         <v>20012</v>
       </c>
       <c r="B768" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C768" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D768" s="1" t="s">
         <v>1955</v>
-      </c>
-      <c r="C768" s="1" t="s">
-        <v>1956</v>
-      </c>
-      <c r="D768" s="1" t="s">
-        <v>1957</v>
       </c>
     </row>
     <row r="769" spans="1:5">
@@ -19698,13 +19937,13 @@
         <v>20013</v>
       </c>
       <c r="B769" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C769" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D769" s="1" t="s">
         <v>1958</v>
-      </c>
-      <c r="C769" s="1" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D769" s="1" t="s">
-        <v>1960</v>
       </c>
     </row>
     <row r="770" spans="1:5">
@@ -19712,13 +19951,13 @@
         <v>20014</v>
       </c>
       <c r="B770" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C770" s="1" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D770" s="1" t="s">
         <v>1961</v>
-      </c>
-      <c r="C770" s="1" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D770" s="1" t="s">
-        <v>1963</v>
       </c>
     </row>
     <row r="771" spans="1:5">
@@ -19726,13 +19965,13 @@
         <v>20015</v>
       </c>
       <c r="B771" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C771" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D771" s="1" t="s">
         <v>1964</v>
-      </c>
-      <c r="C771" s="1" t="s">
-        <v>1965</v>
-      </c>
-      <c r="D771" s="1" t="s">
-        <v>1966</v>
       </c>
     </row>
     <row r="772" spans="1:5">
@@ -19740,13 +19979,13 @@
         <v>20016</v>
       </c>
       <c r="B772" s="1" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C772" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D772" s="1" t="s">
         <v>1967</v>
-      </c>
-      <c r="C772" s="1" t="s">
-        <v>1968</v>
-      </c>
-      <c r="D772" s="1" t="s">
-        <v>1969</v>
       </c>
     </row>
     <row r="773" spans="1:5">
@@ -19754,13 +19993,13 @@
         <v>20017</v>
       </c>
       <c r="B773" s="1" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C773" s="1" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D773" s="1" t="s">
         <v>1970</v>
-      </c>
-      <c r="C773" s="1" t="s">
-        <v>1971</v>
-      </c>
-      <c r="D773" s="1" t="s">
-        <v>1972</v>
       </c>
     </row>
     <row r="774" spans="1:5">
@@ -19768,13 +20007,13 @@
         <v>20018</v>
       </c>
       <c r="B774" s="1" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C774" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D774" s="1" t="s">
         <v>1973</v>
-      </c>
-      <c r="C774" s="1" t="s">
-        <v>1974</v>
-      </c>
-      <c r="D774" s="1" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="775" spans="1:5">
@@ -19782,16 +20021,16 @@
         <v>20019</v>
       </c>
       <c r="B775" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C775" s="1" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E775" s="1" t="s">
         <v>1976</v>
-      </c>
-      <c r="C775" s="1" t="s">
-        <v>1977</v>
-      </c>
-      <c r="D775" s="1" t="s">
-        <v>1979</v>
-      </c>
-      <c r="E775" s="1" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="776" spans="1:5">
@@ -19799,16 +20038,16 @@
         <v>20020</v>
       </c>
       <c r="B776" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C776" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D776" s="1" t="s">
         <v>1980</v>
       </c>
-      <c r="C776" s="1" t="s">
+      <c r="E776" s="1" t="s">
         <v>1981</v>
-      </c>
-      <c r="D776" s="1" t="s">
-        <v>1982</v>
-      </c>
-      <c r="E776" s="1" t="s">
-        <v>1983</v>
       </c>
     </row>
     <row r="777" spans="1:5">
@@ -19816,13 +20055,13 @@
         <v>20021</v>
       </c>
       <c r="B777" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C777" s="1" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D777" s="1" t="s">
         <v>1984</v>
-      </c>
-      <c r="C777" s="1" t="s">
-        <v>1985</v>
-      </c>
-      <c r="D777" s="1" t="s">
-        <v>1986</v>
       </c>
     </row>
     <row r="778" spans="1:5">
@@ -19830,13 +20069,13 @@
         <v>20022</v>
       </c>
       <c r="B778" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C778" s="1" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D778" s="1" t="s">
         <v>1987</v>
-      </c>
-      <c r="C778" s="1" t="s">
-        <v>1988</v>
-      </c>
-      <c r="D778" s="1" t="s">
-        <v>1989</v>
       </c>
     </row>
     <row r="779" spans="1:5">
@@ -19844,13 +20083,13 @@
         <v>20023</v>
       </c>
       <c r="B779" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D779" s="1" t="s">
         <v>1990</v>
-      </c>
-      <c r="C779" s="1" t="s">
-        <v>1991</v>
-      </c>
-      <c r="D779" s="1" t="s">
-        <v>1992</v>
       </c>
     </row>
     <row r="780" spans="1:5">
@@ -19858,13 +20097,13 @@
         <v>20024</v>
       </c>
       <c r="B780" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C780" s="1" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D780" s="1" t="s">
         <v>1993</v>
-      </c>
-      <c r="C780" s="1" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D780" s="1" t="s">
-        <v>1995</v>
       </c>
     </row>
     <row r="781" spans="1:5">
@@ -19872,16 +20111,16 @@
         <v>20025</v>
       </c>
       <c r="B781" s="1" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C781" s="1" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D781" s="1" t="s">
         <v>1996</v>
       </c>
-      <c r="C781" s="1" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D781" s="1" t="s">
-        <v>1999</v>
-      </c>
       <c r="E781" s="1" t="s">
-        <v>1998</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="782" spans="1:5">
@@ -19889,16 +20128,16 @@
         <v>20026</v>
       </c>
       <c r="B782" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C782" s="1" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D782" s="1" t="s">
         <v>2000</v>
       </c>
-      <c r="C782" s="1" t="s">
-        <v>2001</v>
-      </c>
-      <c r="D782" s="1" t="s">
-        <v>2003</v>
-      </c>
       <c r="E782" s="1" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="783" spans="1:5">
@@ -19906,13 +20145,13 @@
         <v>20027</v>
       </c>
       <c r="B783" s="1" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C783" s="1" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="D783" s="1" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="784" spans="1:5">
@@ -19923,13 +20162,13 @@
         <v>249</v>
       </c>
       <c r="C784" s="1" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="D784" s="1" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="E784" s="1" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="785" spans="1:5">
@@ -19937,13 +20176,13 @@
         <v>20029</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C785" s="1" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="D785" s="1" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="786" spans="1:5">
@@ -19951,13 +20190,13 @@
         <v>20030</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C786" s="1" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="D786" s="1" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="787" spans="1:5">
@@ -19965,13 +20204,13 @@
         <v>20031</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C787" s="1" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D787" s="1" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="788" spans="1:5">
@@ -19979,13 +20218,13 @@
         <v>20032</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C788" s="1" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D788" s="1" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="789" spans="1:5">
@@ -19993,16 +20232,16 @@
         <v>20033</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C789" s="1" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D789" s="1" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="E789" s="1" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="790" spans="1:5">
@@ -20010,13 +20249,13 @@
         <v>20034</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C790" s="1" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D790" s="1" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="791" spans="1:5">
@@ -20024,13 +20263,13 @@
         <v>20035</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="C791" s="1" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D791" s="1" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="792" spans="1:5">
@@ -20038,13 +20277,13 @@
         <v>20036</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
       <c r="C792" s="1" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="D792" s="1" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="793" spans="1:5">
@@ -20052,13 +20291,13 @@
         <v>20037</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="C793" s="1" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="D793" s="1" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="794" spans="1:5">
@@ -20066,13 +20305,13 @@
         <v>20038</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="C794" s="1" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="D794" s="1" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="795" spans="1:5">
@@ -20080,13 +20319,13 @@
         <v>20039</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="C795" s="1" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="D795" s="1" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="796" spans="1:5">
@@ -20094,16 +20333,16 @@
         <v>20040</v>
       </c>
       <c r="B796" s="1" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C796" s="1" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E796" s="1" t="s">
         <v>2043</v>
-      </c>
-      <c r="C796" s="1" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D796" s="1" t="s">
-        <v>2045</v>
-      </c>
-      <c r="E796" s="1" t="s">
-        <v>2046</v>
       </c>
     </row>
     <row r="797" spans="1:5">
@@ -20111,13 +20350,13 @@
         <v>20041</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="C797" s="1" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="D797" s="1" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="798" spans="1:5">
@@ -20125,13 +20364,13 @@
         <v>20042</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
       <c r="C798" s="1" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="D798" s="1" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="799" spans="1:5">
@@ -20139,27 +20378,27 @@
         <v>20043</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
       <c r="C799" s="1" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
       <c r="D799" s="1" t="s">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="800" spans="1:5" ht="27.75">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="800" spans="1:5" ht="28">
       <c r="A800" s="1">
         <v>21001</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
       <c r="D800" s="2" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="801" spans="1:5">
@@ -20167,13 +20406,13 @@
         <v>21002</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="C801" s="1" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="D801" s="1" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="802" spans="1:5">
@@ -20181,55 +20420,55 @@
         <v>21003</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="C802" s="1" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
       <c r="D802" s="1" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="803" spans="1:5" ht="27.75">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="803" spans="1:5" ht="28">
       <c r="A803" s="1">
         <v>21004</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="D803" s="2" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="804" spans="1:5" ht="27.75">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="804" spans="1:5" ht="28">
       <c r="A804" s="1">
         <v>21005</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="D804" s="2" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="805" spans="1:5" ht="27.75">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="805" spans="1:5" ht="28">
       <c r="A805" s="1">
         <v>21006</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="D805" s="2" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="806" spans="1:5">
@@ -20237,27 +20476,27 @@
         <v>21007</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="C806" s="1" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
       <c r="D806" s="1" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="807" spans="1:5" ht="27.75">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="807" spans="1:5" ht="28">
       <c r="A807" s="1">
         <v>21008</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="D807" s="2" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="808" spans="1:5">
@@ -20265,55 +20504,55 @@
         <v>21009</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="C808" s="1" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="D808" s="1" t="s">
-        <v>2082</v>
-      </c>
-    </row>
-    <row r="809" spans="1:5" ht="27.75">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="809" spans="1:5" ht="28">
       <c r="A809" s="1">
         <v>21010</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="C809" s="2" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="D809" s="2" t="s">
-        <v>2085</v>
-      </c>
-    </row>
-    <row r="810" spans="1:5" ht="27.75">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="810" spans="1:5" ht="28">
       <c r="A810" s="1">
         <v>21011</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="D810" s="2" t="s">
-        <v>2088</v>
-      </c>
-    </row>
-    <row r="811" spans="1:5" ht="27.75">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="811" spans="1:5" ht="28">
       <c r="A811" s="1">
         <v>21012</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="D811" s="2" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="812" spans="1:5">
@@ -20321,16 +20560,16 @@
         <v>21013</v>
       </c>
       <c r="B812" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C812" s="1" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D812" s="1" t="s">
         <v>2092</v>
       </c>
-      <c r="C812" s="1" t="s">
-        <v>2093</v>
-      </c>
-      <c r="D812" s="1" t="s">
-        <v>2095</v>
-      </c>
       <c r="E812" s="1" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="813" spans="1:5">
@@ -20338,13 +20577,13 @@
         <v>21014</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="C813" s="1" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="D813" s="1" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="814" spans="1:5">
@@ -20352,16 +20591,16 @@
         <v>21015</v>
       </c>
       <c r="B814" s="1" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C814" s="1" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D814" s="1" t="s">
         <v>2099</v>
       </c>
-      <c r="C814" s="1" t="s">
-        <v>2101</v>
-      </c>
-      <c r="D814" s="1" t="s">
-        <v>2102</v>
-      </c>
       <c r="E814" s="1" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="815" spans="1:5">
@@ -20369,13 +20608,13 @@
         <v>21016</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="C815" s="1" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="D815" s="1" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="816" spans="1:5">
@@ -20383,228 +20622,285 @@
         <v>21017</v>
       </c>
       <c r="B816" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C816" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D816" s="1" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5">
+      <c r="A817" s="1">
+        <v>21018</v>
+      </c>
+      <c r="B817" s="1" t="s">
         <v>2106</v>
-      </c>
-      <c r="C816" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D816" s="1" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="817" spans="2:5">
-      <c r="B817" s="1" t="s">
-        <v>2109</v>
       </c>
       <c r="C817" s="1" t="s">
         <v>434</v>
       </c>
       <c r="D817" s="1" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="818" spans="1:5">
+      <c r="A818" s="1">
+        <v>21019</v>
+      </c>
+      <c r="B818" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C818" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D818" s="1" t="s">
         <v>2110</v>
       </c>
     </row>
-    <row r="818" spans="2:5">
-      <c r="B818" s="1" t="s">
+    <row r="819" spans="1:5">
+      <c r="A819" s="1">
+        <v>21020</v>
+      </c>
+      <c r="B819" s="1" t="s">
         <v>2111</v>
       </c>
-      <c r="C818" s="1" t="s">
+      <c r="C819" s="1" t="s">
         <v>2112</v>
       </c>
-      <c r="D818" s="1" t="s">
+      <c r="D819" s="1" t="s">
         <v>2113</v>
       </c>
     </row>
-    <row r="819" spans="2:5">
-      <c r="B819" s="1" t="s">
+    <row r="820" spans="1:5">
+      <c r="A820" s="1">
+        <v>21021</v>
+      </c>
+      <c r="B820" s="1" t="s">
         <v>2114</v>
       </c>
-      <c r="C819" s="1" t="s">
+      <c r="C820" s="1" t="s">
         <v>2115</v>
       </c>
-      <c r="D819" s="1" t="s">
+      <c r="D820" s="1" t="s">
         <v>2116</v>
       </c>
     </row>
-    <row r="820" spans="2:5">
-      <c r="B820" s="1" t="s">
+    <row r="821" spans="1:5">
+      <c r="A821" s="1">
+        <v>21022</v>
+      </c>
+      <c r="B821" s="1" t="s">
         <v>2117</v>
       </c>
-      <c r="C820" s="1" t="s">
+      <c r="C821" s="1" t="s">
         <v>2118</v>
       </c>
-      <c r="D820" s="1" t="s">
+      <c r="D821" s="1" t="s">
         <v>2119</v>
       </c>
     </row>
-    <row r="821" spans="2:5">
-      <c r="B821" s="1" t="s">
-        <v>2120</v>
-      </c>
-      <c r="C821" s="1" t="s">
-        <v>2121</v>
-      </c>
-      <c r="D821" s="1" t="s">
-        <v>2122</v>
-      </c>
-    </row>
-    <row r="822" spans="2:5">
+    <row r="822" spans="1:5">
+      <c r="A822" s="1">
+        <v>21023</v>
+      </c>
       <c r="B822" s="1" t="s">
         <v>444</v>
       </c>
       <c r="C822" s="1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="823" spans="1:5">
+      <c r="A823" s="1">
+        <v>21024</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C823" s="1" t="s">
         <v>2123</v>
       </c>
-      <c r="D822" s="1" t="s">
+      <c r="D823" s="1" t="s">
         <v>2124</v>
       </c>
     </row>
-    <row r="823" spans="2:5">
-      <c r="B823" s="1" t="s">
+    <row r="824" spans="1:5">
+      <c r="A824" s="1">
+        <v>21025</v>
+      </c>
+      <c r="B824" s="1" t="s">
         <v>2125</v>
       </c>
-      <c r="C823" s="1" t="s">
+      <c r="C824" s="1" t="s">
         <v>2126</v>
       </c>
-      <c r="D823" s="1" t="s">
+      <c r="D824" s="1" t="s">
         <v>2127</v>
       </c>
     </row>
-    <row r="824" spans="2:5">
-      <c r="B824" s="1" t="s">
+    <row r="825" spans="1:5">
+      <c r="A825" s="1">
+        <v>21026</v>
+      </c>
+      <c r="B825" s="1" t="s">
         <v>2128</v>
       </c>
-      <c r="C824" s="1" t="s">
+      <c r="C825" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E825" s="1" t="s">
         <v>2129</v>
       </c>
-      <c r="D824" s="1" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="825" spans="2:5">
-      <c r="B825" s="1" t="s">
-        <v>2131</v>
-      </c>
-      <c r="C825" s="1" t="s">
+    </row>
+    <row r="826" spans="1:5">
+      <c r="A826" s="1">
+        <v>21027</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D826" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="D825" s="1" t="s">
-        <v>2134</v>
-      </c>
-      <c r="E825" s="1" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="826" spans="2:5">
-      <c r="B826" s="1" t="s">
+    </row>
+    <row r="827" spans="1:5">
+      <c r="A827" s="1">
+        <v>21028</v>
+      </c>
+      <c r="B827" s="1" t="s">
         <v>2135</v>
       </c>
-      <c r="C826" s="1" t="s">
+      <c r="C827" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="D827" s="1" t="s">
         <v>2137</v>
       </c>
-      <c r="D826" s="1" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="827" spans="2:5">
-      <c r="B827" s="1" t="s">
+    </row>
+    <row r="828" spans="1:5">
+      <c r="A828" s="1">
+        <v>21029</v>
+      </c>
+      <c r="B828" s="1" t="s">
         <v>2138</v>
       </c>
-      <c r="C827" s="1" t="s">
+      <c r="C828" s="1" t="s">
         <v>2139</v>
       </c>
-      <c r="D827" s="1" t="s">
+      <c r="D828" s="1" t="s">
         <v>2140</v>
       </c>
     </row>
-    <row r="828" spans="2:5">
-      <c r="B828" s="1" t="s">
+    <row r="829" spans="1:5">
+      <c r="A829" s="1">
+        <v>21030</v>
+      </c>
+      <c r="B829" s="1" t="s">
         <v>2141</v>
       </c>
-      <c r="C828" s="1" t="s">
+      <c r="C829" s="1" t="s">
         <v>2142</v>
       </c>
-      <c r="D828" s="1" t="s">
+      <c r="D829" s="1" t="s">
         <v>2143</v>
       </c>
-    </row>
-    <row r="829" spans="2:5">
-      <c r="B829" s="1" t="s">
+      <c r="E829" s="1" t="s">
         <v>2144</v>
       </c>
-      <c r="C829" s="1" t="s">
+    </row>
+    <row r="830" spans="1:5">
+      <c r="A830" s="1">
+        <v>21031</v>
+      </c>
+      <c r="B830" s="1" t="s">
         <v>2145</v>
       </c>
-      <c r="D829" s="1" t="s">
+      <c r="C830" s="1" t="s">
         <v>2146</v>
       </c>
-      <c r="E829" s="1" t="s">
+      <c r="D830" s="1" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="830" spans="2:5">
-      <c r="B830" s="1" t="s">
+    <row r="831" spans="1:5">
+      <c r="A831" s="1">
+        <v>21032</v>
+      </c>
+      <c r="B831" s="1" t="s">
         <v>2148</v>
       </c>
-      <c r="C830" s="1" t="s">
+      <c r="C831" s="1" t="s">
         <v>2149</v>
       </c>
-      <c r="D830" s="1" t="s">
+      <c r="D831" s="1" t="s">
         <v>2150</v>
       </c>
     </row>
-    <row r="831" spans="2:5">
-      <c r="B831" s="1" t="s">
+    <row r="832" spans="1:5">
+      <c r="A832" s="1">
+        <v>21033</v>
+      </c>
+      <c r="B832" s="1" t="s">
         <v>2151</v>
       </c>
-      <c r="C831" s="1" t="s">
+      <c r="C832" s="1" t="s">
         <v>2152</v>
       </c>
-      <c r="D831" s="1" t="s">
+      <c r="D832" s="1" t="s">
         <v>2153</v>
       </c>
     </row>
-    <row r="832" spans="2:5">
-      <c r="B832" s="1" t="s">
+    <row r="833" spans="1:4">
+      <c r="A833" s="1">
+        <v>21034</v>
+      </c>
+      <c r="B833" s="1" t="s">
         <v>2154</v>
       </c>
-      <c r="C832" s="1" t="s">
+      <c r="C833" s="1" t="s">
         <v>2155</v>
       </c>
-      <c r="D832" s="1" t="s">
+      <c r="D833" s="1" t="s">
         <v>2156</v>
       </c>
     </row>
-    <row r="833" spans="2:4">
-      <c r="B833" s="1" t="s">
+    <row r="834" spans="1:4">
+      <c r="A834" s="1">
+        <v>21035</v>
+      </c>
+      <c r="B834" s="1" t="s">
         <v>2157</v>
       </c>
-      <c r="C833" s="1" t="s">
+      <c r="C834" s="1" t="s">
         <v>2158</v>
       </c>
-      <c r="D833" s="1" t="s">
+      <c r="D834" s="1" t="s">
         <v>2159</v>
       </c>
     </row>
-    <row r="834" spans="2:4">
-      <c r="B834" s="1" t="s">
+    <row r="835" spans="1:4">
+      <c r="A835" s="1">
+        <v>21036</v>
+      </c>
+      <c r="B835" s="1" t="s">
         <v>2160</v>
       </c>
-      <c r="C834" s="1" t="s">
+      <c r="C835" s="1" t="s">
         <v>2161</v>
       </c>
-      <c r="D834" s="1" t="s">
+      <c r="D835" s="1" t="s">
         <v>2162</v>
-      </c>
-    </row>
-    <row r="835" spans="2:4">
-      <c r="B835" s="1" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C835" s="1" t="s">
-        <v>2164</v>
-      </c>
-      <c r="D835" s="1" t="s">
-        <v>2165</v>
       </c>
     </row>
   </sheetData>
@@ -20615,13 +20911,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BEDC60-BD86-4F0B-8906-B631C56865DE}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.73046875" customWidth="1"/>
-    <col min="4" max="4" width="15.9296875" customWidth="1"/>
-    <col min="5" max="5" width="52.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.9140625" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="15.9140625" customWidth="1"/>
+    <col min="5" max="5" width="52.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20654,56 +20950,56 @@
     </row>
     <row r="3" spans="1:5">
       <c r="B3" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="C3" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D4" t="s">
         <v>1579</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1580</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="C5" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D6" t="s">
         <v>1584</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1585</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C7" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="C8" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -20711,34 +21007,208 @@
         <v>1164</v>
       </c>
       <c r="C9" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="C10" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="C11" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
       <c r="C12" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
       <c r="E12" t="s">
-        <v>2177</v>
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" t="s">
+        <v>2238</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2245</v>
       </c>
     </row>
   </sheetData>
@@ -20749,11 +21219,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D070E02D-D4DA-4042-9E24-5FF12F571A9A}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="12.19921875" customWidth="1"/>
-    <col min="3" max="3" width="14.19921875" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="23.6640625" customWidth="1"/>
   </cols>
@@ -20777,24 +21247,82 @@
     </row>
     <row r="2" spans="1:5">
       <c r="B2" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="C2" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="D2" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="C3" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="D3" t="s">
-        <v>2184</v>
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2223</v>
       </c>
     </row>
   </sheetData>
@@ -20806,10 +21334,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E327196-0A94-422A-A422-84A769DDFF6A}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="3" width="16.06640625" customWidth="1"/>
-    <col min="5" max="5" width="31.796875" customWidth="1"/>
+    <col min="2" max="3" width="16.08203125" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20885,10 +21413,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="C8" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
     </row>
   </sheetData>
